--- a/ListasDatos/Camarillo Aburto Raymundo_2021.xlsx
+++ b/ListasDatos/Camarillo Aburto Raymundo_2021.xlsx
@@ -8,18 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="3ARHV" sheetId="1" r:id="rId1"/>
-    <sheet name="3APV" sheetId="2" r:id="rId2"/>
-    <sheet name="3ASV" sheetId="3" r:id="rId3"/>
-    <sheet name="3BEM" sheetId="4" r:id="rId4"/>
-    <sheet name="3BLCM" sheetId="5" r:id="rId5"/>
-    <sheet name="3APM" sheetId="6" r:id="rId6"/>
+    <sheet name="3ASV" sheetId="2" r:id="rId2"/>
+    <sheet name="3BEM" sheetId="3" r:id="rId3"/>
+    <sheet name="3BLCM" sheetId="4" r:id="rId4"/>
+    <sheet name="3APM" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="1206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="1069">
   <si>
     <t>NC</t>
   </si>
@@ -813,2377 +812,1966 @@
     <t>2721264468</t>
   </si>
   <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>BENITEZ</t>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MAYA</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAID</t>
+  </si>
+  <si>
+    <t>DIANA ITZEL</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>JESUS SAMUEL</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>ARIZBETH</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>FRANCISCO YAEL</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>KELLY ITZEL</t>
+  </si>
+  <si>
+    <t>MICHELLE ROBERTA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>JAQUELINE</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
+    <t>xxcatgdxx@gmail.com</t>
+  </si>
+  <si>
+    <t>bmo10star@gmail.com</t>
+  </si>
+  <si>
+    <t>dianitaitzelbonillatepepa@gmail.com</t>
+  </si>
+  <si>
+    <t>asunakirigayav@gmail.com</t>
+  </si>
+  <si>
+    <t>ctsuri97@gmail.com</t>
+  </si>
+  <si>
+    <t>marcosflow285@gmail.com</t>
+  </si>
+  <si>
+    <t>erikaleonpalacios7@gmail.com</t>
+  </si>
+  <si>
+    <t>roger123459876@gmail.com</t>
+  </si>
+  <si>
+    <t>Arizbethhernandez37@gmail.com</t>
+  </si>
+  <si>
+    <t>veracruzcampeon@gmail.com</t>
+  </si>
+  <si>
+    <t>emmanuelnightmare70@gmail.com</t>
+  </si>
+  <si>
+    <t>jl0250315@gmail.com</t>
+  </si>
+  <si>
+    <t>ymaya210@gmail.com</t>
+  </si>
+  <si>
+    <t>irvingmolina722@gmail.com</t>
+  </si>
+  <si>
+    <t>vr7001887@gmail.com</t>
+  </si>
+  <si>
+    <t>juan.najmon@hotmail.com</t>
+  </si>
+  <si>
+    <t>oziel_1711@hotmail.com</t>
+  </si>
+  <si>
+    <t>riverakelly283@gmail.com</t>
+  </si>
+  <si>
+    <t>michelle.romero221005@gmail.com</t>
+  </si>
+  <si>
+    <t>manolodg54@gmail.com</t>
+  </si>
+  <si>
+    <t>jaquelintexcahua@gmail.com</t>
+  </si>
+  <si>
+    <t>doriluz28plm@gmail.com</t>
+  </si>
+  <si>
+    <t>2723030256</t>
+  </si>
+  <si>
+    <t>2712643206</t>
+  </si>
+  <si>
+    <t>2722835035</t>
+  </si>
+  <si>
+    <t>2722830478</t>
+  </si>
+  <si>
+    <t>2722424689</t>
+  </si>
+  <si>
+    <t>2712066034</t>
+  </si>
+  <si>
+    <t>2722955934</t>
+  </si>
+  <si>
+    <t>2722487227</t>
+  </si>
+  <si>
+    <t>2721943860</t>
+  </si>
+  <si>
+    <t>2727012892</t>
+  </si>
+  <si>
+    <t>2721875560</t>
+  </si>
+  <si>
+    <t>2722464777</t>
+  </si>
+  <si>
+    <t>2722605858</t>
+  </si>
+  <si>
+    <t>2723036382</t>
+  </si>
+  <si>
+    <t>2722359505</t>
+  </si>
+  <si>
+    <t>2721825175</t>
+  </si>
+  <si>
+    <t>2721889661</t>
+  </si>
+  <si>
+    <t>2722109030</t>
+  </si>
+  <si>
+    <t>2721871808</t>
+  </si>
+  <si>
+    <t>2721918415</t>
+  </si>
+  <si>
+    <t>2722836200</t>
+  </si>
+  <si>
+    <t>2726883887</t>
+  </si>
+  <si>
+    <t>2722174569</t>
+  </si>
+  <si>
+    <t>2721473515</t>
+  </si>
+  <si>
+    <t>2721577811</t>
+  </si>
+  <si>
+    <t>2722173953</t>
+  </si>
+  <si>
+    <t>2721105587</t>
+  </si>
+  <si>
+    <t>2721154206</t>
+  </si>
+  <si>
+    <t>2721330685</t>
+  </si>
+  <si>
+    <t>2721150883</t>
+  </si>
+  <si>
+    <t>2722016136</t>
+  </si>
+  <si>
+    <t>JOSÉ APALE ROSALES</t>
+  </si>
+  <si>
+    <t>MIGUEL ÁNGEL RAMÍREZ MORENO</t>
+  </si>
+  <si>
+    <t>GUADALUPE ITZEL TEPEPA ROSAS</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL CANTELLAN CARRERA</t>
+  </si>
+  <si>
+    <t>JOSE Y UBALDO COCOTLE VIVAS</t>
+  </si>
+  <si>
+    <t>OSCAR HERNÁNDEZ HERNÁNDEZ</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS GARCIA ROSA</t>
+  </si>
+  <si>
+    <t>ROGELIO GAMEZ BAZ</t>
+  </si>
+  <si>
+    <t>ELIAS GONZALEZ SALINAS</t>
+  </si>
+  <si>
+    <t>EMIR DAVID HERNANDEZ TOLEDO</t>
+  </si>
+  <si>
+    <t>JORGE ARISTEO IBAÑEZ HUERTA</t>
+  </si>
+  <si>
+    <t>ISABEL MORALES MARTINEZ</t>
+  </si>
+  <si>
+    <t>KARINA BAEZA HERNÁNDEZ</t>
+  </si>
+  <si>
+    <t>MIRIAM MOLINA MORALES</t>
+  </si>
+  <si>
+    <t>ANTONIA ROCIO RODRÍGUEZ SANCHEZ</t>
+  </si>
+  <si>
+    <t>NORA LILIANA NAJERA MONTALVO</t>
+  </si>
+  <si>
+    <t>OSCAR OCAÑA MEDINA</t>
+  </si>
+  <si>
+    <t>NOÉ RIVERA CRUZ</t>
+  </si>
+  <si>
+    <t>JESÚS ROMERO FLORES</t>
+  </si>
+  <si>
+    <t>JOSE LUIS SANCHEZ VELASQUEZ</t>
+  </si>
+  <si>
+    <t>ERICK TEXCAHUA TRUJILLO</t>
+  </si>
+  <si>
+    <t>CRISTINA TZITZIHUA HERNÁNDEZ</t>
+  </si>
+  <si>
+    <t>Joseapale@gmail.com</t>
+  </si>
+  <si>
+    <t>miguel.li.ke@hotmail.com</t>
+  </si>
+  <si>
+    <t>guadalupeitseltepeparosas@gmail.com</t>
+  </si>
+  <si>
+    <t>manu730518@hotmail.com</t>
+  </si>
+  <si>
+    <t>Oscarhernandez1327@gmail.com</t>
+  </si>
+  <si>
+    <t>mies_proyectos@hotmail.com</t>
+  </si>
+  <si>
+    <t>bazroger25@gmail.com</t>
+  </si>
+  <si>
+    <t>Crizzhernandez885@gmail.com</t>
+  </si>
+  <si>
+    <t>Emirdavidhernandez@gmail.com</t>
+  </si>
+  <si>
+    <t>Saorimartinez57@gmail.com</t>
+  </si>
+  <si>
+    <t>karinahbz1202@gmail.com</t>
+  </si>
+  <si>
+    <t>miriam235molina@gmail.com</t>
+  </si>
+  <si>
+    <t>victorrodriguez7073@gmail.com</t>
+  </si>
+  <si>
+    <t>manuel.flomat@hotmail.com</t>
+  </si>
+  <si>
+    <t>Kelly_rivera_vargas@gmail.com</t>
+  </si>
+  <si>
+    <t>jesus_ramirez_flores@outlook.com</t>
+  </si>
+  <si>
+    <t>MHH_MAU@hotmail.com</t>
+  </si>
+  <si>
+    <t>lmjadl22z@gmail.com</t>
+  </si>
+  <si>
+    <t>2721315051</t>
+  </si>
+  <si>
+    <t>2723034348</t>
+  </si>
+  <si>
+    <t>2711487522</t>
+  </si>
+  <si>
+    <t>2297716300</t>
+  </si>
+  <si>
+    <t>2722105724</t>
+  </si>
+  <si>
+    <t>2781222268</t>
+  </si>
+  <si>
+    <t>2721008951</t>
+  </si>
+  <si>
+    <t>2721995168</t>
+  </si>
+  <si>
+    <t>2727194835</t>
+  </si>
+  <si>
+    <t>2721245362</t>
+  </si>
+  <si>
+    <t>2722808516</t>
+  </si>
+  <si>
+    <t>2722450135</t>
+  </si>
+  <si>
+    <t>2721883803</t>
+  </si>
+  <si>
+    <t>2294199965</t>
+  </si>
+  <si>
+    <t>2722614304</t>
+  </si>
+  <si>
+    <t>2721563464</t>
+  </si>
+  <si>
+    <t>2722368326</t>
+  </si>
+  <si>
+    <t>2721671051</t>
+  </si>
+  <si>
+    <t>2721961051</t>
+  </si>
+  <si>
+    <t>2722367270</t>
+  </si>
+  <si>
+    <t>2721314323</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>ANASTACIO</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>GARCÍA</t>
+  </si>
+  <si>
+    <t>CONCHOA</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>HIRAM FABIAN</t>
+  </si>
+  <si>
+    <t>RAUL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>MARIA ASUNCION</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>NOEL ALBERTO</t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>CESAR OMAR</t>
+  </si>
+  <si>
+    <t>ROSA ISELA</t>
+  </si>
+  <si>
+    <t>BENY ALEXANDER</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>gusalvarez2005@outlook.com</t>
+  </si>
+  <si>
+    <t>alan.amador.444@gmail.com</t>
+  </si>
+  <si>
+    <t>hiramromero161@gmail.com</t>
+  </si>
+  <si>
+    <t>ruletaaguilar0905@gmail.com</t>
+  </si>
+  <si>
+    <t>urielabril404@gmail.com</t>
+  </si>
+  <si>
+    <t>misaelcitalan132@gmail.com</t>
+  </si>
+  <si>
+    <t>cidjesus994@gmail.com</t>
+  </si>
+  <si>
+    <t>colohuadavid39@gmail.com</t>
+  </si>
+  <si>
+    <t>delacruzyahir17@gmail.com</t>
+  </si>
+  <si>
+    <t>jcm1234jcm1234@gmail.com</t>
+  </si>
+  <si>
+    <t>dbrunoazael@gmail.com</t>
+  </si>
+  <si>
+    <t>cf593364@gmail.com</t>
+  </si>
+  <si>
+    <t>asunciongarcia2603@mail.com</t>
+  </si>
+  <si>
+    <t>frijolito952@gmail.com</t>
+  </si>
+  <si>
+    <t>ghrobertin2005@gmail.com</t>
+  </si>
+  <si>
+    <t>noelalbertogonzalezvelazquez@gmail.com</t>
+  </si>
+  <si>
+    <t>lg6395271@gmail.com</t>
+  </si>
+  <si>
+    <t>adrimark28@gmail.com</t>
+  </si>
+  <si>
+    <t>aldairalan101@gmail.com</t>
+  </si>
+  <si>
+    <t>mendi2004.ab@gmail.com</t>
+  </si>
+  <si>
+    <t>antonionajera537@gmail.com</t>
+  </si>
+  <si>
+    <t>najeraisaac81@gmail.com</t>
+  </si>
+  <si>
+    <t>cristhiannardo@gmail.com</t>
+  </si>
+  <si>
+    <t>sergiotiburon9@gmail.com</t>
+  </si>
+  <si>
+    <t>ivanolmos281@hotmail.com</t>
+  </si>
+  <si>
+    <t>jc15rami@gmail.com</t>
+  </si>
+  <si>
+    <t>cesarroh99@gmail.com</t>
+  </si>
+  <si>
+    <t>snchezisela5@gmail.com</t>
+  </si>
+  <si>
+    <t>iv8067515@gmail.com</t>
+  </si>
+  <si>
+    <t>abiudvalente7@gmail.com</t>
+  </si>
+  <si>
+    <t>guillermo19vs@gmail.com</t>
+  </si>
+  <si>
+    <t>alexanderxotlanihua94@gmail.com</t>
+  </si>
+  <si>
+    <t>2721112218</t>
+  </si>
+  <si>
+    <t>2722270353</t>
+  </si>
+  <si>
+    <t>2722344361</t>
+  </si>
+  <si>
+    <t>2722144339</t>
+  </si>
+  <si>
+    <t>2722975473</t>
+  </si>
+  <si>
+    <t>2722611268</t>
+  </si>
+  <si>
+    <t>2722588412</t>
+  </si>
+  <si>
+    <t>2722363253</t>
+  </si>
+  <si>
+    <t>2721279595</t>
+  </si>
+  <si>
+    <t>2721951012</t>
+  </si>
+  <si>
+    <t>2722848871</t>
+  </si>
+  <si>
+    <t>2721999093</t>
+  </si>
+  <si>
+    <t>2722291678</t>
+  </si>
+  <si>
+    <t>2721398447</t>
+  </si>
+  <si>
+    <t>2722302121</t>
+  </si>
+  <si>
+    <t>2711396180</t>
+  </si>
+  <si>
+    <t>2722812284</t>
+  </si>
+  <si>
+    <t>2721753318</t>
+  </si>
+  <si>
+    <t>2722796584</t>
+  </si>
+  <si>
+    <t>2722459333</t>
+  </si>
+  <si>
+    <t>2722844764</t>
+  </si>
+  <si>
+    <t>2722960713</t>
+  </si>
+  <si>
+    <t>2721138420</t>
+  </si>
+  <si>
+    <t>2721930581</t>
+  </si>
+  <si>
+    <t>2722830361</t>
+  </si>
+  <si>
+    <t>2721330497</t>
+  </si>
+  <si>
+    <t>2721978228</t>
+  </si>
+  <si>
+    <t>2722259377</t>
+  </si>
+  <si>
+    <t>2722305627</t>
+  </si>
+  <si>
+    <t>2722834971</t>
+  </si>
+  <si>
+    <t>2727849544</t>
+  </si>
+  <si>
+    <t>2722255802</t>
+  </si>
+  <si>
+    <t>2721711929</t>
+  </si>
+  <si>
+    <t>2721828353</t>
+  </si>
+  <si>
+    <t>2727210160</t>
+  </si>
+  <si>
+    <t>2721522194</t>
+  </si>
+  <si>
+    <t>2727211730</t>
+  </si>
+  <si>
+    <t>2721347690</t>
+  </si>
+  <si>
+    <t>2727840074</t>
+  </si>
+  <si>
+    <t>2722333638</t>
+  </si>
+  <si>
+    <t>2726885171</t>
+  </si>
+  <si>
+    <t>2722432231</t>
+  </si>
+  <si>
+    <t>2721715018</t>
+  </si>
+  <si>
+    <t>2722333266</t>
+  </si>
+  <si>
+    <t>9711271360</t>
+  </si>
+  <si>
+    <t>2721909303</t>
+  </si>
+  <si>
+    <t>2722012284</t>
+  </si>
+  <si>
+    <t>JOSE MAURICIO ALVAREZ VEGA</t>
+  </si>
+  <si>
+    <t>MARIO JESÚS AMADOR CASTRO</t>
+  </si>
+  <si>
+    <t>ANTELMO ANASTACIO ROMERO</t>
+  </si>
+  <si>
+    <t>RAUL AGUILAR ORTIZ</t>
+  </si>
+  <si>
+    <t>MARIA ELVIRA CHONCOA ATLAHUA</t>
+  </si>
+  <si>
+    <t>MISAEL CITALAN SANCHEZ</t>
+  </si>
+  <si>
+    <t>ROBERTO CID VALENCIA</t>
+  </si>
+  <si>
+    <t>JACOBO COLOHUA SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>FLORENCIO ALBERTO DE LA CRUZ MONTER</t>
+  </si>
+  <si>
+    <t>ERASTO CRUZ MARTÍNEZ</t>
+  </si>
+  <si>
+    <t>SIMÓN ANSELMO DÍAZ ROSAS</t>
+  </si>
+  <si>
+    <t>GABINA FLORES SEGURA</t>
+  </si>
+  <si>
+    <t>JULIO CÉSAR GARCÍA CERÓN</t>
+  </si>
+  <si>
+    <t>LIBERTAD GUADALUPE FLORES FERNÁNDEZ</t>
+  </si>
+  <si>
+    <t>FERNANDO GÓMEZ HERNÁNDEZ</t>
+  </si>
+  <si>
+    <t>FILIBERTO GONZALEZ AGUILAR</t>
+  </si>
+  <si>
+    <t>MOISES PEREZ GUEVARA</t>
+  </si>
+  <si>
+    <t>ADRIÁN HERNÁNDEZ VEGA</t>
+  </si>
+  <si>
+    <t>ANDRÉS DE JESÚS NOE</t>
+  </si>
+  <si>
+    <t>GIOVANNI HERNÁNDEZ HERRERA</t>
+  </si>
+  <si>
+    <t>MATEO NÁJERA DOMÍNGUEZ</t>
+  </si>
+  <si>
+    <t>MATEO NAJERA DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>SALVADOR NUBE MARTÍNEZ</t>
+  </si>
+  <si>
+    <t>JULIETA ROSETE MALDONADO</t>
+  </si>
+  <si>
+    <t>HIGINIO OLMOS ESTÉVEZ</t>
+  </si>
+  <si>
+    <t>ROSENDO RAMIREZ ANTONIO</t>
+  </si>
+  <si>
+    <t>CÁNDIDO RODRÍGUEZ JUÁREZ</t>
+  </si>
+  <si>
+    <t>FEDERICO SANCHEZ SALAZAR</t>
+  </si>
+  <si>
+    <t>CLARIBEL VALENCIA RODRÍGUEZ</t>
+  </si>
+  <si>
+    <t>CLARA GAMEZ VÁSQUEZ</t>
+  </si>
+  <si>
+    <t>FLORENCIO VASQUEZ PONCE</t>
+  </si>
+  <si>
+    <t>MARIBEL XOTLANIHUA TEXCAHUA</t>
+  </si>
+  <si>
+    <t>jomaalve@outlook.com</t>
+  </si>
+  <si>
+    <t>anthelmo2512@outlook.es</t>
+  </si>
+  <si>
+    <t>raulao@hotmail.com</t>
+  </si>
+  <si>
+    <t>Urielabril404@gmail.com</t>
+  </si>
+  <si>
+    <t>evelincitalanromanos@gmail.com</t>
+  </si>
+  <si>
+    <t>doloresvalencia0908@gmail.com</t>
+  </si>
+  <si>
+    <t>albertodelacruz119@gmail.com</t>
+  </si>
+  <si>
+    <t>guadalajara20002@hotmail.com</t>
+  </si>
+  <si>
+    <t>julio1214094@gmail.com</t>
+  </si>
+  <si>
+    <t>marcogf234@gmail.com</t>
+  </si>
+  <si>
+    <t>Lic.fergo@outlook.com</t>
+  </si>
+  <si>
+    <t>gonzalezfiliberto020@gmail.com</t>
+  </si>
+  <si>
+    <t>diana_hdz_0901@hotmail.com</t>
+  </si>
+  <si>
+    <t>isabelevaristo6@gmail.com</t>
+  </si>
+  <si>
+    <t>giovanni2604@hotmail.com</t>
+  </si>
+  <si>
+    <t>najeraantonio342@gmail.com</t>
+  </si>
+  <si>
+    <t>najeraisaac81@gamil.com</t>
+  </si>
+  <si>
+    <t>salvadornubes@gmail.com</t>
+  </si>
+  <si>
+    <t>olmos_28@outlook.com</t>
+  </si>
+  <si>
+    <t>canrgz02@gmail.com</t>
+  </si>
+  <si>
+    <t>Valenciaclaribel28@gmail.com</t>
+  </si>
+  <si>
+    <t>Gamezclara580@gmail.com</t>
+  </si>
+  <si>
+    <t>alex11glez@gmail.com</t>
+  </si>
+  <si>
+    <t>mari.1976.xt@gmail.com</t>
+  </si>
+  <si>
+    <t>2722339631</t>
+  </si>
+  <si>
+    <t>2723349050</t>
+  </si>
+  <si>
+    <t>2722065477</t>
+  </si>
+  <si>
+    <t>2721028416</t>
+  </si>
+  <si>
+    <t>2721049711</t>
+  </si>
+  <si>
+    <t>2722104360</t>
+  </si>
+  <si>
+    <t>5584511583</t>
+  </si>
+  <si>
+    <t>2721958449</t>
+  </si>
+  <si>
+    <t>2722827558</t>
+  </si>
+  <si>
+    <t>2723030755</t>
+  </si>
+  <si>
+    <t>2722040299</t>
+  </si>
+  <si>
+    <t>2727056086</t>
+  </si>
+  <si>
+    <t>2727221390</t>
+  </si>
+  <si>
+    <t>2717116527</t>
+  </si>
+  <si>
+    <t>2711856309</t>
+  </si>
+  <si>
+    <t>2721438411</t>
+  </si>
+  <si>
+    <t>2721884428</t>
+  </si>
+  <si>
+    <t>2721018853</t>
+  </si>
+  <si>
+    <t>2722298675</t>
+  </si>
+  <si>
+    <t>2727059466</t>
+  </si>
+  <si>
+    <t>2721078507</t>
+  </si>
+  <si>
+    <t>2721286728</t>
+  </si>
+  <si>
+    <t>2721988471</t>
+  </si>
+  <si>
+    <t>2721309981</t>
+  </si>
+  <si>
+    <t>2721495946</t>
+  </si>
+  <si>
+    <t>2721765782</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>CARAZA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>CAMARILLO</t>
+  </si>
+  <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
   </si>
   <si>
     <t>DE LUNA</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>MIRAFUENTES</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>NAVARRO</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>ZUNO</t>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>CANSINO</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>ROBRES</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>ARENZANO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>KAREN ESTEPHANY</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CITLALLI</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
+    <t>JARED URIEL</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>ARIZBET</t>
+  </si>
+  <si>
+    <t>VALERIA ANGELY</t>
+  </si>
+  <si>
+    <t>STEPHANIE</t>
+  </si>
+  <si>
+    <t>SIARI DANAHY</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>YAMILE</t>
+  </si>
+  <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>ELIAN</t>
+  </si>
+  <si>
+    <t>MARIA MAGDALENA</t>
+  </si>
+  <si>
+    <t>IKER</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>JOSE ISAAC</t>
+  </si>
+  <si>
+    <t>IVONNE SHERLINE</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>RITA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>SAMANTHA</t>
+  </si>
+  <si>
+    <t>ARANTZA</t>
+  </si>
+  <si>
+    <t>DULCE MARIA</t>
+  </si>
+  <si>
+    <t>MARIA XIMENA</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
+    <t>ZULEICA RENATA</t>
+  </si>
+  <si>
+    <t>JOSELIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANEL</t>
+  </si>
+  <si>
+    <t>LAURA IVETTE</t>
+  </si>
+  <si>
+    <t>altamiranokaren999@gmail.com</t>
+  </si>
+  <si>
+    <t>isanga0805@gmail.com</t>
+  </si>
+  <si>
+    <t>arroyocitlalli@hotmail.com</t>
+  </si>
+  <si>
+    <t>guapotamichelle@gmail.com</t>
+  </si>
+  <si>
+    <t>Timy.caraza.cruz@gmail.com</t>
+  </si>
+  <si>
+    <t>danielcargz@gmail.com</t>
+  </si>
+  <si>
+    <t>arielcamarillo76@gmail.com</t>
+  </si>
+  <si>
+    <t>vcruzcansino@gmail.com</t>
+  </si>
+  <si>
+    <t>valeryangel26@gmail.com</t>
+  </si>
+  <si>
+    <t>stephaniegasca92@gmail.com</t>
+  </si>
+  <si>
+    <t>siaridanahygaliciapaz@gmail.com</t>
+  </si>
+  <si>
+    <t>aztequitatupapi@gmail.com</t>
+  </si>
+  <si>
+    <t>herrera12berth@gmail.com</t>
+  </si>
+  <si>
+    <t>alexapradoh@gmail.com</t>
+  </si>
+  <si>
+    <t>ariadnaramirez162@gmail.com</t>
+  </si>
+  <si>
+    <t>elianleyva14@gmail.com</t>
+  </si>
+  <si>
+    <t>nina.mmlm@gamil.com</t>
+  </si>
+  <si>
+    <t>1k3rd3lun4@gmail.com</t>
+  </si>
+  <si>
+    <t>santilop493@gmail.com</t>
+  </si>
+  <si>
+    <t>josemart041020@gmail.com</t>
+  </si>
+  <si>
+    <t>griselserrano11218@gmail.com</t>
+  </si>
+  <si>
+    <t>jesusenrique122004@gmail.com</t>
+  </si>
+  <si>
+    <t>cambelsaguilar@gmail.com</t>
+  </si>
+  <si>
+    <t>alejandranavarrorobles0503@gmail.com</t>
+  </si>
+  <si>
+    <t>marianaperezmorales17@gmail.com</t>
+  </si>
+  <si>
+    <t>marisolrs800@gmail.com</t>
+  </si>
+  <si>
+    <t>ramoszepedasamantha@gmail.com</t>
+  </si>
+  <si>
+    <t>arantzar33@gmail.com</t>
+  </si>
+  <si>
+    <t>rojas.2004.dulce15@gmail.com</t>
+  </si>
+  <si>
+    <t>santilu0505@gmail.com</t>
+  </si>
+  <si>
+    <t>ntorrescarrera@gmail.com</t>
+  </si>
+  <si>
+    <t>renicarrasco75@gmail.com</t>
+  </si>
+  <si>
+    <t>joselintorres79123@gmail.com</t>
+  </si>
+  <si>
+    <t>tabaniarenzano@gmail.com</t>
+  </si>
+  <si>
+    <t>faluivette03@gmail.com</t>
+  </si>
+  <si>
+    <t>2721222536</t>
+  </si>
+  <si>
+    <t>2721698901</t>
+  </si>
+  <si>
+    <t>2722821050</t>
+  </si>
+  <si>
+    <t>2721089340</t>
+  </si>
+  <si>
+    <t>2722960589</t>
+  </si>
+  <si>
+    <t>2721383983</t>
+  </si>
+  <si>
+    <t>2722468972</t>
+  </si>
+  <si>
+    <t>2721706496</t>
+  </si>
+  <si>
+    <t>2727843492</t>
+  </si>
+  <si>
+    <t>2721586212</t>
+  </si>
+  <si>
+    <t>2723354956</t>
+  </si>
+  <si>
+    <t>2722628012</t>
+  </si>
+  <si>
+    <t>2721350028</t>
+  </si>
+  <si>
+    <t>2721138149</t>
+  </si>
+  <si>
+    <t>2721578705</t>
+  </si>
+  <si>
+    <t>2722595581</t>
+  </si>
+  <si>
+    <t>2721179455</t>
+  </si>
+  <si>
+    <t>2722600861</t>
+  </si>
+  <si>
+    <t>2722805311</t>
+  </si>
+  <si>
+    <t>2721342134</t>
+  </si>
+  <si>
+    <t>2721633478</t>
+  </si>
+  <si>
+    <t>2721966360</t>
+  </si>
+  <si>
+    <t>2725729386</t>
+  </si>
+  <si>
+    <t>2721207603</t>
+  </si>
+  <si>
+    <t>2721282076</t>
+  </si>
+  <si>
+    <t>2722426314</t>
+  </si>
+  <si>
+    <t>2721926504</t>
+  </si>
+  <si>
+    <t>2722337199</t>
+  </si>
+  <si>
+    <t>2722960143</t>
+  </si>
+  <si>
+    <t>2721413122</t>
+  </si>
+  <si>
+    <t>2722044505</t>
+  </si>
+  <si>
+    <t>2721315316</t>
+  </si>
+  <si>
+    <t>2721201026</t>
+  </si>
+  <si>
+    <t>2722293076</t>
+  </si>
+  <si>
+    <t>2722841219</t>
+  </si>
+  <si>
+    <t>2727213347</t>
+  </si>
+  <si>
+    <t>2721712859</t>
+  </si>
+  <si>
+    <t>2712753922</t>
+  </si>
+  <si>
+    <t>2721474215</t>
+  </si>
+  <si>
+    <t>2722174055</t>
+  </si>
+  <si>
+    <t>2726883799</t>
+  </si>
+  <si>
+    <t>2722356724</t>
+  </si>
+  <si>
+    <t>2722108990</t>
+  </si>
+  <si>
+    <t>2722110166</t>
+  </si>
+  <si>
+    <t>2721056621</t>
+  </si>
+  <si>
+    <t>2722018470</t>
+  </si>
+  <si>
+    <t>2726880117</t>
+  </si>
+  <si>
+    <t>2727213395</t>
+  </si>
+  <si>
+    <t>2722456652</t>
+  </si>
+  <si>
+    <t>2722110160</t>
+  </si>
+  <si>
+    <t>2722894576</t>
+  </si>
+  <si>
+    <t>2722017247</t>
+  </si>
+  <si>
+    <t>2721712193</t>
+  </si>
+  <si>
+    <t>EVARISTO ALTAMIRANO DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>FELIPE ANTONIO REYES</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL ARROYO NAJERA</t>
+  </si>
+  <si>
+    <t>ESTANISLAO ALFONSO CASTRO</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL CARAZA CRUZ</t>
+  </si>
+  <si>
+    <t>FAUSTA RODRÍGUEZ GARCÍA</t>
+  </si>
+  <si>
+    <t>ARIEL CAMARILLO JAIMES</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL CRUZ SIGALA</t>
+  </si>
+  <si>
+    <t>RAYMUNDO FLORES VASQUEZ</t>
+  </si>
+  <si>
+    <t>ESTEBAN GASCA PEREZ</t>
+  </si>
+  <si>
+    <t>RUBEN GALICIA BAUTISTA</t>
+  </si>
+  <si>
+    <t>GONZALO GONZALEZ CASTRO</t>
+  </si>
+  <si>
+    <t>IVÁN HERRERA LUNA</t>
+  </si>
+  <si>
+    <t>CLAUDIA PRADO GARCÍA</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL HERRERA TREJO</t>
+  </si>
+  <si>
+    <t>EFRAÍN LEYVA RAMÍREZ</t>
+  </si>
+  <si>
+    <t>JUAN JOSÉ LÓPEZ CONTRERAS</t>
+  </si>
+  <si>
+    <t>ILIANA CÓRDOVA RICARTE</t>
+  </si>
+  <si>
+    <t>AGUSTIN MARTINEZ CRISTOBAL</t>
+  </si>
+  <si>
+    <t>DANIEL MARTÍNEZ SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>FERNANDO JAIR MALDONADO GONZÁLEZ</t>
+  </si>
+  <si>
+    <t>ENRIQUE MIRAFUENTES TORRES</t>
+  </si>
+  <si>
+    <t>ILIANA AGUILAR MENA</t>
+  </si>
+  <si>
+    <t>LETICIA ROBLES SÁNCHEZ</t>
+  </si>
+  <si>
+    <t>SERGIO PÉREZ HUERTA</t>
+  </si>
+  <si>
+    <t>ROSARIO JUAREZ SANCHEZ</t>
+  </si>
+  <si>
+    <t>SALVADOR RAMOS ZAVALA</t>
+  </si>
+  <si>
+    <t>ELISA REYES PÉREZ</t>
+  </si>
+  <si>
+    <t>EZEQUIEL ROJAS MEDINA</t>
+  </si>
+  <si>
+    <t>MARIO SANTIAGO MENDEZ</t>
+  </si>
+  <si>
+    <t>MARÍA DEL SOCORRO CARRERA HERNÁNDEZ</t>
+  </si>
+  <si>
+    <t>GERMAN TORRES ARIAS</t>
+  </si>
+  <si>
+    <t>IGNACIO MALAQUIAS TORRES CERONIO</t>
+  </si>
+  <si>
+    <t>ARMANDO VENTURA VERA</t>
+  </si>
+  <si>
+    <t>JESUS XOCUA CAMPOS</t>
+  </si>
+  <si>
+    <t>evaristo100680@gmail.com</t>
+  </si>
+  <si>
+    <t>anrefe74@hotmail.com</t>
+  </si>
+  <si>
+    <t>victor_arr97@hotmail.con</t>
+  </si>
+  <si>
+    <t>tanisalfonso8@gmail.com</t>
+  </si>
+  <si>
+    <t>johnny_cruz@hotmail.com</t>
+  </si>
+  <si>
+    <t>faufaurg@gmail.com</t>
+  </si>
+  <si>
+    <t>juanmcruzsigala@gmail.com</t>
+  </si>
+  <si>
+    <t>rayf0352@gmail.com</t>
+  </si>
+  <si>
+    <t>Ruben8405@gmail.com</t>
+  </si>
+  <si>
+    <t>gonzalo713100@gmail.com</t>
+  </si>
+  <si>
+    <t>clauxprado@gmail.com</t>
+  </si>
+  <si>
+    <t>marvic820225@gmail.com</t>
+  </si>
+  <si>
+    <t>Joselopcon2768@gmail.com</t>
+  </si>
+  <si>
+    <t>ilyeudcor@gmail.com</t>
+  </si>
+  <si>
+    <t>Santilop493@gmail.com</t>
+  </si>
+  <si>
+    <t>martisandaniel@gmail.com</t>
+  </si>
+  <si>
+    <t>ferjair71@gmail.com</t>
+  </si>
+  <si>
+    <t>refriespe_786@hotmail.com</t>
+  </si>
+  <si>
+    <t>Cambelsaguilar@gmail.com</t>
+  </si>
+  <si>
+    <t>Perezhuertasergio4@gmail.com</t>
+  </si>
+  <si>
+    <t>samyzepeda15@gmail.com</t>
+  </si>
+  <si>
+    <t>elisareyesperez140@gmal.com</t>
+  </si>
+  <si>
+    <t>mario.san01@hotmail.com</t>
+  </si>
+  <si>
+    <t>Germantorres2504@gmail.com</t>
+  </si>
+  <si>
+    <t>nachitoeyr@gmail.com</t>
+  </si>
+  <si>
+    <t>xventa@hotmail.com</t>
+  </si>
+  <si>
+    <t>sky_ituns_@hotmail.com</t>
+  </si>
+  <si>
+    <t>2727823441</t>
+  </si>
+  <si>
+    <t>27229706655</t>
+  </si>
+  <si>
+    <t>2711481769</t>
+  </si>
+  <si>
+    <t>2721692982</t>
+  </si>
+  <si>
+    <t>2722255234</t>
+  </si>
+  <si>
+    <t>2722030880</t>
+  </si>
+  <si>
+    <t>2721356570</t>
+  </si>
+  <si>
+    <t>2721456231</t>
+  </si>
+  <si>
+    <t>2721644477</t>
+  </si>
+  <si>
+    <t>2721278597</t>
+  </si>
+  <si>
+    <t>2721389978</t>
+  </si>
+  <si>
+    <t>2721116261</t>
+  </si>
+  <si>
+    <t>2721289150</t>
+  </si>
+  <si>
+    <t>9711311117</t>
+  </si>
+  <si>
+    <t>2722956004</t>
+  </si>
+  <si>
+    <t>9921059452</t>
+  </si>
+  <si>
+    <t>2721397474</t>
+  </si>
+  <si>
+    <t>2721340853</t>
+  </si>
+  <si>
+    <t>9211798607</t>
+  </si>
+  <si>
+    <t>2721393961</t>
+  </si>
+  <si>
+    <t>2721821541</t>
+  </si>
+  <si>
+    <t>2721583583</t>
+  </si>
+  <si>
+    <t>2727053277</t>
+  </si>
+  <si>
+    <t>2721917182</t>
+  </si>
+  <si>
+    <t>5588003430</t>
+  </si>
+  <si>
+    <t>2721490103</t>
+  </si>
+  <si>
+    <t>2721386186</t>
+  </si>
+  <si>
+    <t>2721765023</t>
+  </si>
+  <si>
+    <t>2226611097</t>
+  </si>
+  <si>
+    <t>2721976523</t>
+  </si>
+  <si>
+    <t>2721587875</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>URBANO</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>XILCAHUA</t>
+  </si>
+  <si>
+    <t>ATILANO</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>ZAVALETA</t>
   </si>
   <si>
     <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>IAN URIEL</t>
-  </si>
-  <si>
-    <t>LEONARDO GAEL</t>
-  </si>
-  <si>
-    <t>JESUS HUMBERTO</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>AXEL YAEL</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>URIEL ALFREDO</t>
-  </si>
-  <si>
-    <t>ivettecontreras905@gmail.com</t>
-  </si>
-  <si>
-    <t>karenbenbaez05@gmail.com</t>
-  </si>
-  <si>
-    <t>jacastro.rmz@gmail.com</t>
-  </si>
-  <si>
-    <t>sisusuriel812@gmail.com</t>
-  </si>
-  <si>
-    <t>leoelcrackdelfut@gmail.com</t>
-  </si>
-  <si>
-    <t>glezvaleswag@gmail.com</t>
-  </si>
-  <si>
-    <t>gonzalezhumberto020@gmail.com</t>
-  </si>
-  <si>
-    <t>Villa.marti.1011@gmail.com</t>
-  </si>
-  <si>
-    <t>eliashernandezdiaz05@gmail.com</t>
-  </si>
-  <si>
-    <t>karlarenatalc@gmail.com</t>
-  </si>
-  <si>
-    <t>onamlopezsantiago@gmail.com</t>
-  </si>
-  <si>
-    <t>eudydeluna95@gmail.com</t>
-  </si>
-  <si>
-    <t>Mirandalunaflores8@gmail.com</t>
-  </si>
-  <si>
-    <t>danyyiyo23@gmail.com</t>
-  </si>
-  <si>
-    <t>yazminjimenezz506@gmail.com</t>
-  </si>
-  <si>
-    <t>ortiving@gmail.com</t>
-  </si>
-  <si>
-    <t>ramosjosafat29@gmail.com</t>
-  </si>
-  <si>
-    <t>axelyaelsantiagor20.cb192@dgeti.sems.gob.mx</t>
-  </si>
-  <si>
-    <t>marisoltellez431@gmail.com</t>
-  </si>
-  <si>
-    <t>ernestotinoco22@gmail.com</t>
-  </si>
-  <si>
-    <t>urielozuno42@gmail.com</t>
-  </si>
-  <si>
-    <t>2722421732</t>
-  </si>
-  <si>
-    <t>2722971816</t>
-  </si>
-  <si>
-    <t>2722245528</t>
-  </si>
-  <si>
-    <t>2721871229</t>
-  </si>
-  <si>
-    <t>2721412468</t>
-  </si>
-  <si>
-    <t>2721876074</t>
-  </si>
-  <si>
-    <t>2722343127</t>
-  </si>
-  <si>
-    <t>5578467456</t>
-  </si>
-  <si>
-    <t>5530259182</t>
-  </si>
-  <si>
-    <t>2722371602</t>
-  </si>
-  <si>
-    <t>2721019961</t>
-  </si>
-  <si>
-    <t>2722823690</t>
-  </si>
-  <si>
-    <t>2722031314</t>
-  </si>
-  <si>
-    <t>2721342134</t>
-  </si>
-  <si>
-    <t>2722084316</t>
-  </si>
-  <si>
-    <t>2721587712</t>
-  </si>
-  <si>
-    <t>2722356302</t>
-  </si>
-  <si>
-    <t>2722867021</t>
-  </si>
-  <si>
-    <t>2722032602</t>
-  </si>
-  <si>
-    <t>2721078392</t>
-  </si>
-  <si>
-    <t>2721998720</t>
-  </si>
-  <si>
-    <t>2727218250</t>
-  </si>
-  <si>
-    <t>2722971817</t>
-  </si>
-  <si>
-    <t>2726892718</t>
-  </si>
-  <si>
-    <t>5.22722e+16</t>
-  </si>
-  <si>
-    <t>2727211100</t>
-  </si>
-  <si>
-    <t>5581529803</t>
-  </si>
-  <si>
-    <t>2722018470</t>
-  </si>
-  <si>
-    <t>2721061544</t>
-  </si>
-  <si>
-    <t>2721108745</t>
-  </si>
-  <si>
-    <t>2.72721e+16</t>
-  </si>
-  <si>
-    <t>2722111714</t>
-  </si>
-  <si>
-    <t>2721713001</t>
-  </si>
-  <si>
-    <t>JOSE LUIS BALTAZARES REYES</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL BENÍTEZ HERNÁNDEZ</t>
-  </si>
-  <si>
-    <t>JOSÉ DOMINGO CASTRO JUÁREZ</t>
-  </si>
-  <si>
-    <t>LUIS ANTONIO CASTILLO GUZMÁN</t>
-  </si>
-  <si>
-    <t>KARINA GARNICA PINEDA</t>
-  </si>
-  <si>
-    <t>NATALIA ANDRADE RAMÍREZ</t>
-  </si>
-  <si>
-    <t>HUMBERTO GONZÁLEZ PELLICO</t>
-  </si>
-  <si>
-    <t>LUIS GUTIERREZ CORIA</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER HERNANDEZ GONZÁLEZ</t>
-  </si>
-  <si>
-    <t>DAVID ARTURO TEOBAL MONTIEL</t>
-  </si>
-  <si>
-    <t>NORMA AIDA LOPEZ SANTIAGO</t>
-  </si>
-  <si>
-    <t>ILIANA CÓRDOVA RICARTE</t>
-  </si>
-  <si>
-    <t>FELIPE LUNA MOLINA</t>
-  </si>
-  <si>
-    <t>DANIEL MARTINEZ SANCHEZ</t>
-  </si>
-  <si>
-    <t>LUIS OJEDA ZARATE</t>
-  </si>
-  <si>
-    <t>CÉSAR ORTIZ RAMÍREZ</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO RAMOS SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>HÉCTOR IVÁN SANTIAGO CRUZ</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL OFICIAL SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>FERNANDA RAMOS GONZÁLEZ</t>
-  </si>
-  <si>
-    <t>HUGO BÁEZ ROSAS</t>
-  </si>
-  <si>
-    <t>jose_luisbr@hotmail.com</t>
-  </si>
-  <si>
-    <t>Marchate1986@gmail.com</t>
-  </si>
-  <si>
-    <t>jdcastro@gmail.com</t>
-  </si>
-  <si>
-    <t>luis.kaztello@gmail.com</t>
-  </si>
-  <si>
-    <t>garnicakarina825@gmail.com</t>
-  </si>
-  <si>
-    <t>nataliaar691@gmail.com</t>
-  </si>
-  <si>
-    <t>hugonzalezpellico@outlook.com</t>
-  </si>
-  <si>
-    <t>luis.coria.gutierrez45@gmail.com</t>
-  </si>
-  <si>
-    <t>deuss13@gmail.com</t>
-  </si>
-  <si>
-    <t>ORIVER82@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>norma_al_santiago@hotmail.com</t>
-  </si>
-  <si>
-    <t>ilyeudcor@gmail.com</t>
-  </si>
-  <si>
-    <t>felipe1973luna@gmail.com</t>
-  </si>
-  <si>
-    <t>martisandaniel@gmail.com</t>
-  </si>
-  <si>
-    <t>ojedazarateluis@gmail.com</t>
-  </si>
-  <si>
-    <t>Marcoantonio1523@gmail.com</t>
-  </si>
-  <si>
-    <t>banda4203@hotmail.com</t>
-  </si>
-  <si>
-    <t>oficialsanchezmz@gmail.com</t>
-  </si>
-  <si>
-    <t>fernandagonzales2267@gmail.com</t>
-  </si>
-  <si>
-    <t>2721013647</t>
-  </si>
-  <si>
-    <t>2212011630</t>
-  </si>
-  <si>
-    <t>2721675618</t>
-  </si>
-  <si>
-    <t>2727208135</t>
-  </si>
-  <si>
-    <t>2722130712</t>
-  </si>
-  <si>
-    <t>2721224523</t>
-  </si>
-  <si>
-    <t>2721178968</t>
-  </si>
-  <si>
-    <t>5537947446</t>
-  </si>
-  <si>
-    <t>2721230786</t>
-  </si>
-  <si>
-    <t>2721026843</t>
-  </si>
-  <si>
-    <t>2721688255</t>
-  </si>
-  <si>
-    <t>9951059452</t>
-  </si>
-  <si>
-    <t>2727847056</t>
-  </si>
-  <si>
-    <t>2722628018</t>
-  </si>
-  <si>
-    <t>2721625004</t>
-  </si>
-  <si>
-    <t>2721844649</t>
-  </si>
-  <si>
-    <t>2721055481</t>
-  </si>
-  <si>
-    <t>2722865828</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>MAYA</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>DIANA ITZEL</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>JESUS SAMUEL</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>FRANCISCO YAEL</t>
-  </si>
-  <si>
-    <t>IRVING</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
-    <t>KELLY ITZEL</t>
-  </si>
-  <si>
-    <t>MICHELLE ROBERTA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>xxcatgdxx@gmail.com</t>
-  </si>
-  <si>
-    <t>bmo10star@gmail.com</t>
-  </si>
-  <si>
-    <t>dianitaitzelbonillatepepa@gmail.com</t>
-  </si>
-  <si>
-    <t>asunakirigayav@gmail.com</t>
-  </si>
-  <si>
-    <t>ctsuri97@gmail.com</t>
-  </si>
-  <si>
-    <t>marcosflow285@gmail.com</t>
-  </si>
-  <si>
-    <t>erikaleonpalacios7@gmail.com</t>
-  </si>
-  <si>
-    <t>roger123459876@gmail.com</t>
-  </si>
-  <si>
-    <t>Arizbethhernandez37@gmail.com</t>
-  </si>
-  <si>
-    <t>veracruzcampeon@gmail.com</t>
-  </si>
-  <si>
-    <t>emmanuelnightmare70@gmail.com</t>
-  </si>
-  <si>
-    <t>jl0250315@gmail.com</t>
-  </si>
-  <si>
-    <t>ymaya210@gmail.com</t>
-  </si>
-  <si>
-    <t>irvingmolina722@gmail.com</t>
-  </si>
-  <si>
-    <t>vr7001887@gmail.com</t>
-  </si>
-  <si>
-    <t>juan.najmon@hotmail.com</t>
-  </si>
-  <si>
-    <t>oziel_1711@hotmail.com</t>
-  </si>
-  <si>
-    <t>riverakelly283@gmail.com</t>
-  </si>
-  <si>
-    <t>michelle.romero221005@gmail.com</t>
-  </si>
-  <si>
-    <t>manolodg54@gmail.com</t>
-  </si>
-  <si>
-    <t>jaquelintexcahua@gmail.com</t>
-  </si>
-  <si>
-    <t>doriluz28plm@gmail.com</t>
-  </si>
-  <si>
-    <t>2723030256</t>
-  </si>
-  <si>
-    <t>2712643206</t>
-  </si>
-  <si>
-    <t>2722835035</t>
-  </si>
-  <si>
-    <t>2722830478</t>
-  </si>
-  <si>
-    <t>2722424689</t>
-  </si>
-  <si>
-    <t>2712066034</t>
-  </si>
-  <si>
-    <t>2722955934</t>
-  </si>
-  <si>
-    <t>2722487227</t>
-  </si>
-  <si>
-    <t>2721943860</t>
-  </si>
-  <si>
-    <t>2727012892</t>
-  </si>
-  <si>
-    <t>2721875560</t>
-  </si>
-  <si>
-    <t>2722464777</t>
-  </si>
-  <si>
-    <t>2722605858</t>
-  </si>
-  <si>
-    <t>2723036382</t>
-  </si>
-  <si>
-    <t>2722359505</t>
-  </si>
-  <si>
-    <t>2721825175</t>
-  </si>
-  <si>
-    <t>2721889661</t>
-  </si>
-  <si>
-    <t>2722109030</t>
-  </si>
-  <si>
-    <t>2721871808</t>
-  </si>
-  <si>
-    <t>2721918415</t>
-  </si>
-  <si>
-    <t>2722836200</t>
-  </si>
-  <si>
-    <t>2726883887</t>
-  </si>
-  <si>
-    <t>2722174569</t>
-  </si>
-  <si>
-    <t>2721473515</t>
-  </si>
-  <si>
-    <t>2721577811</t>
-  </si>
-  <si>
-    <t>2722173953</t>
-  </si>
-  <si>
-    <t>2721105587</t>
-  </si>
-  <si>
-    <t>2721154206</t>
-  </si>
-  <si>
-    <t>2721330685</t>
-  </si>
-  <si>
-    <t>2721150883</t>
-  </si>
-  <si>
-    <t>2722016136</t>
-  </si>
-  <si>
-    <t>JOSÉ APALE ROSALES</t>
-  </si>
-  <si>
-    <t>MIGUEL ÁNGEL RAMÍREZ MORENO</t>
-  </si>
-  <si>
-    <t>GUADALUPE ITZEL TEPEPA ROSAS</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL CANTELLAN CARRERA</t>
-  </si>
-  <si>
-    <t>JOSE Y UBALDO COCOTLE VIVAS</t>
-  </si>
-  <si>
-    <t>OSCAR HERNÁNDEZ HERNÁNDEZ</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS GARCIA ROSA</t>
-  </si>
-  <si>
-    <t>ROGELIO GAMEZ BAZ</t>
-  </si>
-  <si>
-    <t>ELIAS GONZALEZ SALINAS</t>
-  </si>
-  <si>
-    <t>EMIR DAVID HERNANDEZ TOLEDO</t>
-  </si>
-  <si>
-    <t>JORGE ARISTEO IBAÑEZ HUERTA</t>
-  </si>
-  <si>
-    <t>ISABEL MORALES MARTINEZ</t>
-  </si>
-  <si>
-    <t>KARINA BAEZA HERNÁNDEZ</t>
-  </si>
-  <si>
-    <t>MIRIAM MOLINA MORALES</t>
-  </si>
-  <si>
-    <t>ANTONIA ROCIO RODRÍGUEZ SANCHEZ</t>
-  </si>
-  <si>
-    <t>NORA LILIANA NAJERA MONTALVO</t>
-  </si>
-  <si>
-    <t>OSCAR OCAÑA MEDINA</t>
-  </si>
-  <si>
-    <t>NOÉ RIVERA CRUZ</t>
-  </si>
-  <si>
-    <t>JESÚS ROMERO FLORES</t>
-  </si>
-  <si>
-    <t>JOSE LUIS SANCHEZ VELASQUEZ</t>
-  </si>
-  <si>
-    <t>ERICK TEXCAHUA TRUJILLO</t>
-  </si>
-  <si>
-    <t>CRISTINA TZITZIHUA HERNÁNDEZ</t>
-  </si>
-  <si>
-    <t>Joseapale@gmail.com</t>
-  </si>
-  <si>
-    <t>miguel.li.ke@hotmail.com</t>
-  </si>
-  <si>
-    <t>guadalupeitseltepeparosas@gmail.com</t>
-  </si>
-  <si>
-    <t>manu730518@hotmail.com</t>
-  </si>
-  <si>
-    <t>Oscarhernandez1327@gmail.com</t>
-  </si>
-  <si>
-    <t>mies_proyectos@hotmail.com</t>
-  </si>
-  <si>
-    <t>bazroger25@gmail.com</t>
-  </si>
-  <si>
-    <t>Crizzhernandez885@gmail.com</t>
-  </si>
-  <si>
-    <t>Emirdavidhernandez@gmail.com</t>
-  </si>
-  <si>
-    <t>Saorimartinez57@gmail.com</t>
-  </si>
-  <si>
-    <t>karinahbz1202@gmail.com</t>
-  </si>
-  <si>
-    <t>miriam235molina@gmail.com</t>
-  </si>
-  <si>
-    <t>victorrodriguez7073@gmail.com</t>
-  </si>
-  <si>
-    <t>manuel.flomat@hotmail.com</t>
-  </si>
-  <si>
-    <t>Kelly_rivera_vargas@gmail.com</t>
-  </si>
-  <si>
-    <t>jesus_ramirez_flores@outlook.com</t>
-  </si>
-  <si>
-    <t>MHH_MAU@hotmail.com</t>
-  </si>
-  <si>
-    <t>lmjadl22z@gmail.com</t>
-  </si>
-  <si>
-    <t>2721315051</t>
-  </si>
-  <si>
-    <t>2723034348</t>
-  </si>
-  <si>
-    <t>2711487522</t>
-  </si>
-  <si>
-    <t>2297716300</t>
-  </si>
-  <si>
-    <t>2722105724</t>
-  </si>
-  <si>
-    <t>2781222268</t>
-  </si>
-  <si>
-    <t>2721008951</t>
-  </si>
-  <si>
-    <t>2721995168</t>
-  </si>
-  <si>
-    <t>2727194835</t>
-  </si>
-  <si>
-    <t>2721245362</t>
-  </si>
-  <si>
-    <t>2722808516</t>
-  </si>
-  <si>
-    <t>2722450135</t>
-  </si>
-  <si>
-    <t>2721883803</t>
-  </si>
-  <si>
-    <t>2294199965</t>
-  </si>
-  <si>
-    <t>2722614304</t>
-  </si>
-  <si>
-    <t>2721563464</t>
-  </si>
-  <si>
-    <t>2722368326</t>
-  </si>
-  <si>
-    <t>2721671051</t>
-  </si>
-  <si>
-    <t>2721961051</t>
-  </si>
-  <si>
-    <t>2722367270</t>
-  </si>
-  <si>
-    <t>2721314323</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>ANASTACIO</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>GARCÍA</t>
-  </si>
-  <si>
-    <t>CONCHOA</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>HIRAM FABIAN</t>
-  </si>
-  <si>
-    <t>RAUL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>MARIA ASUNCION</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>NOEL ALBERTO</t>
-  </si>
-  <si>
-    <t>LUIS ALBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>CESAR OMAR</t>
-  </si>
-  <si>
-    <t>ROSA ISELA</t>
-  </si>
-  <si>
-    <t>BENY ALEXANDER</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>gusalvarez2005@outlook.com</t>
-  </si>
-  <si>
-    <t>alan.amador.444@gmail.com</t>
-  </si>
-  <si>
-    <t>hiramromero161@gmail.com</t>
-  </si>
-  <si>
-    <t>ruletaaguilar0905@gmail.com</t>
-  </si>
-  <si>
-    <t>urielabril404@gmail.com</t>
-  </si>
-  <si>
-    <t>misaelcitalan132@gmail.com</t>
-  </si>
-  <si>
-    <t>cidjesus994@gmail.com</t>
-  </si>
-  <si>
-    <t>colohuadavid39@gmail.com</t>
-  </si>
-  <si>
-    <t>delacruzyahir17@gmail.com</t>
-  </si>
-  <si>
-    <t>jcm1234jcm1234@gmail.com</t>
-  </si>
-  <si>
-    <t>dbrunoazael@gmail.com</t>
-  </si>
-  <si>
-    <t>cf593364@gmail.com</t>
-  </si>
-  <si>
-    <t>asunciongarcia2603@mail.com</t>
-  </si>
-  <si>
-    <t>frijolito952@gmail.com</t>
-  </si>
-  <si>
-    <t>ghrobertin2005@gmail.com</t>
-  </si>
-  <si>
-    <t>noelalbertogonzalezvelazquez@gmail.com</t>
-  </si>
-  <si>
-    <t>lg6395271@gmail.com</t>
-  </si>
-  <si>
-    <t>adrimark28@gmail.com</t>
-  </si>
-  <si>
-    <t>aldairalan101@gmail.com</t>
-  </si>
-  <si>
-    <t>mendi2004.ab@gmail.com</t>
-  </si>
-  <si>
-    <t>antonionajera537@gmail.com</t>
-  </si>
-  <si>
-    <t>najeraisaac81@gmail.com</t>
-  </si>
-  <si>
-    <t>cristhiannardo@gmail.com</t>
-  </si>
-  <si>
-    <t>sergiotiburon9@gmail.com</t>
-  </si>
-  <si>
-    <t>ivanolmos281@hotmail.com</t>
-  </si>
-  <si>
-    <t>jc15rami@gmail.com</t>
-  </si>
-  <si>
-    <t>cesarroh99@gmail.com</t>
-  </si>
-  <si>
-    <t>snchezisela5@gmail.com</t>
-  </si>
-  <si>
-    <t>iv8067515@gmail.com</t>
-  </si>
-  <si>
-    <t>abiudvalente7@gmail.com</t>
-  </si>
-  <si>
-    <t>guillermo19vs@gmail.com</t>
-  </si>
-  <si>
-    <t>alexanderxotlanihua94@gmail.com</t>
-  </si>
-  <si>
-    <t>2721112218</t>
-  </si>
-  <si>
-    <t>2722270353</t>
-  </si>
-  <si>
-    <t>2722344361</t>
-  </si>
-  <si>
-    <t>2722144339</t>
-  </si>
-  <si>
-    <t>2722975473</t>
-  </si>
-  <si>
-    <t>2722611268</t>
-  </si>
-  <si>
-    <t>2722588412</t>
-  </si>
-  <si>
-    <t>2722363253</t>
-  </si>
-  <si>
-    <t>2721279595</t>
-  </si>
-  <si>
-    <t>2721951012</t>
-  </si>
-  <si>
-    <t>2722848871</t>
-  </si>
-  <si>
-    <t>2721999093</t>
-  </si>
-  <si>
-    <t>2722291678</t>
-  </si>
-  <si>
-    <t>2721398447</t>
-  </si>
-  <si>
-    <t>2722302121</t>
-  </si>
-  <si>
-    <t>2711396180</t>
-  </si>
-  <si>
-    <t>2722812284</t>
-  </si>
-  <si>
-    <t>2721753318</t>
-  </si>
-  <si>
-    <t>2722796584</t>
-  </si>
-  <si>
-    <t>2722459333</t>
-  </si>
-  <si>
-    <t>2722844764</t>
-  </si>
-  <si>
-    <t>2722960713</t>
-  </si>
-  <si>
-    <t>2721138420</t>
-  </si>
-  <si>
-    <t>2721930581</t>
-  </si>
-  <si>
-    <t>2722830361</t>
-  </si>
-  <si>
-    <t>2721330497</t>
-  </si>
-  <si>
-    <t>2721978228</t>
-  </si>
-  <si>
-    <t>2722259377</t>
-  </si>
-  <si>
-    <t>2722305627</t>
-  </si>
-  <si>
-    <t>2722834971</t>
-  </si>
-  <si>
-    <t>2727849544</t>
-  </si>
-  <si>
-    <t>2722255802</t>
-  </si>
-  <si>
-    <t>2721711929</t>
-  </si>
-  <si>
-    <t>2721828353</t>
-  </si>
-  <si>
-    <t>2727210160</t>
-  </si>
-  <si>
-    <t>2721522194</t>
-  </si>
-  <si>
-    <t>2727211730</t>
-  </si>
-  <si>
-    <t>2721347690</t>
-  </si>
-  <si>
-    <t>2727840074</t>
-  </si>
-  <si>
-    <t>2722333638</t>
-  </si>
-  <si>
-    <t>2726885171</t>
-  </si>
-  <si>
-    <t>2722432231</t>
-  </si>
-  <si>
-    <t>2721715018</t>
-  </si>
-  <si>
-    <t>2722333266</t>
-  </si>
-  <si>
-    <t>9711271360</t>
-  </si>
-  <si>
-    <t>2721909303</t>
-  </si>
-  <si>
-    <t>2722012284</t>
-  </si>
-  <si>
-    <t>JOSE MAURICIO ALVAREZ VEGA</t>
-  </si>
-  <si>
-    <t>MARIO JESÚS AMADOR CASTRO</t>
-  </si>
-  <si>
-    <t>ANTELMO ANASTACIO ROMERO</t>
-  </si>
-  <si>
-    <t>RAUL AGUILAR ORTIZ</t>
-  </si>
-  <si>
-    <t>MARIA ELVIRA CHONCOA ATLAHUA</t>
-  </si>
-  <si>
-    <t>MISAEL CITALAN SANCHEZ</t>
-  </si>
-  <si>
-    <t>ROBERTO CID VALENCIA</t>
-  </si>
-  <si>
-    <t>JACOBO COLOHUA SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>FLORENCIO ALBERTO DE LA CRUZ MONTER</t>
-  </si>
-  <si>
-    <t>ERASTO CRUZ MARTÍNEZ</t>
-  </si>
-  <si>
-    <t>SIMÓN ANSELMO DÍAZ ROSAS</t>
-  </si>
-  <si>
-    <t>GABINA FLORES SEGURA</t>
-  </si>
-  <si>
-    <t>JULIO CÉSAR GARCÍA CERÓN</t>
-  </si>
-  <si>
-    <t>LIBERTAD GUADALUPE FLORES FERNÁNDEZ</t>
-  </si>
-  <si>
-    <t>FERNANDO GÓMEZ HERNÁNDEZ</t>
-  </si>
-  <si>
-    <t>FILIBERTO GONZALEZ AGUILAR</t>
-  </si>
-  <si>
-    <t>MOISES PEREZ GUEVARA</t>
-  </si>
-  <si>
-    <t>ADRIÁN HERNÁNDEZ VEGA</t>
-  </si>
-  <si>
-    <t>ANDRÉS DE JESÚS NOE</t>
-  </si>
-  <si>
-    <t>GIOVANNI HERNÁNDEZ HERRERA</t>
-  </si>
-  <si>
-    <t>MATEO NÁJERA DOMÍNGUEZ</t>
-  </si>
-  <si>
-    <t>MATEO NAJERA DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>SALVADOR NUBE MARTÍNEZ</t>
-  </si>
-  <si>
-    <t>JULIETA ROSETE MALDONADO</t>
-  </si>
-  <si>
-    <t>HIGINIO OLMOS ESTÉVEZ</t>
-  </si>
-  <si>
-    <t>ROSENDO RAMIREZ ANTONIO</t>
-  </si>
-  <si>
-    <t>CÁNDIDO RODRÍGUEZ JUÁREZ</t>
-  </si>
-  <si>
-    <t>FEDERICO SANCHEZ SALAZAR</t>
-  </si>
-  <si>
-    <t>CLARIBEL VALENCIA RODRÍGUEZ</t>
-  </si>
-  <si>
-    <t>CLARA GAMEZ VÁSQUEZ</t>
-  </si>
-  <si>
-    <t>FLORENCIO VASQUEZ PONCE</t>
-  </si>
-  <si>
-    <t>MARIBEL XOTLANIHUA TEXCAHUA</t>
-  </si>
-  <si>
-    <t>jomaalve@outlook.com</t>
-  </si>
-  <si>
-    <t>anthelmo2512@outlook.es</t>
-  </si>
-  <si>
-    <t>raulao@hotmail.com</t>
-  </si>
-  <si>
-    <t>Urielabril404@gmail.com</t>
-  </si>
-  <si>
-    <t>evelincitalanromanos@gmail.com</t>
-  </si>
-  <si>
-    <t>doloresvalencia0908@gmail.com</t>
-  </si>
-  <si>
-    <t>albertodelacruz119@gmail.com</t>
-  </si>
-  <si>
-    <t>guadalajara20002@hotmail.com</t>
-  </si>
-  <si>
-    <t>julio1214094@gmail.com</t>
-  </si>
-  <si>
-    <t>marcogf234@gmail.com</t>
-  </si>
-  <si>
-    <t>Lic.fergo@outlook.com</t>
-  </si>
-  <si>
-    <t>gonzalezfiliberto020@gmail.com</t>
-  </si>
-  <si>
-    <t>diana_hdz_0901@hotmail.com</t>
-  </si>
-  <si>
-    <t>isabelevaristo6@gmail.com</t>
-  </si>
-  <si>
-    <t>giovanni2604@hotmail.com</t>
-  </si>
-  <si>
-    <t>najeraantonio342@gmail.com</t>
-  </si>
-  <si>
-    <t>najeraisaac81@gamil.com</t>
-  </si>
-  <si>
-    <t>salvadornubes@gmail.com</t>
-  </si>
-  <si>
-    <t>olmos_28@outlook.com</t>
-  </si>
-  <si>
-    <t>canrgz02@gmail.com</t>
-  </si>
-  <si>
-    <t>Valenciaclaribel28@gmail.com</t>
-  </si>
-  <si>
-    <t>Gamezclara580@gmail.com</t>
-  </si>
-  <si>
-    <t>alex11glez@gmail.com</t>
-  </si>
-  <si>
-    <t>mari.1976.xt@gmail.com</t>
-  </si>
-  <si>
-    <t>2722339631</t>
-  </si>
-  <si>
-    <t>2723349050</t>
-  </si>
-  <si>
-    <t>2722065477</t>
-  </si>
-  <si>
-    <t>2721028416</t>
-  </si>
-  <si>
-    <t>2721049711</t>
-  </si>
-  <si>
-    <t>2722104360</t>
-  </si>
-  <si>
-    <t>5584511583</t>
-  </si>
-  <si>
-    <t>2721958449</t>
-  </si>
-  <si>
-    <t>2722827558</t>
-  </si>
-  <si>
-    <t>2723030755</t>
-  </si>
-  <si>
-    <t>2722040299</t>
-  </si>
-  <si>
-    <t>2727056086</t>
-  </si>
-  <si>
-    <t>2727221390</t>
-  </si>
-  <si>
-    <t>2717116527</t>
-  </si>
-  <si>
-    <t>2711856309</t>
-  </si>
-  <si>
-    <t>2721438411</t>
-  </si>
-  <si>
-    <t>2721884428</t>
-  </si>
-  <si>
-    <t>2721018853</t>
-  </si>
-  <si>
-    <t>2722298675</t>
-  </si>
-  <si>
-    <t>2727059466</t>
-  </si>
-  <si>
-    <t>2721078507</t>
-  </si>
-  <si>
-    <t>2721286728</t>
-  </si>
-  <si>
-    <t>2721988471</t>
-  </si>
-  <si>
-    <t>2721309981</t>
-  </si>
-  <si>
-    <t>2721495946</t>
-  </si>
-  <si>
-    <t>2721765782</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>CARAZA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>CAMARILLO</t>
-  </si>
-  <si>
-    <t>GASCA</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MIRAFUENTES</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>CANSINO</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>PRADO</t>
-  </si>
-  <si>
-    <t>MONTERROSAS</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>ROBRES</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>ARENZANO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>KAREN ESTEPHANY</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>CITLALLI</t>
-  </si>
-  <si>
-    <t>AMERICA MICHELLE</t>
-  </si>
-  <si>
-    <t>JARED URIEL</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>ARIZBET</t>
-  </si>
-  <si>
-    <t>VALERIA ANGELY</t>
-  </si>
-  <si>
-    <t>STEPHANIE</t>
-  </si>
-  <si>
-    <t>SIARI DANAHY</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>YAMILE</t>
-  </si>
-  <si>
-    <t>ALEXA</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>ELIAN</t>
-  </si>
-  <si>
-    <t>MARIA MAGDALENA</t>
-  </si>
-  <si>
-    <t>IKER</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>JOSE ISAAC</t>
-  </si>
-  <si>
-    <t>IVONNE SHERLINE</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>RITA ALEJANDRA</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>SAMANTHA</t>
-  </si>
-  <si>
-    <t>ARANTZA</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>MARIA XIMENA</t>
-  </si>
-  <si>
-    <t>NAOMI</t>
-  </si>
-  <si>
-    <t>ZULEICA RENATA</t>
-  </si>
-  <si>
-    <t>JOSELIN GUADALUPE</t>
-  </si>
-  <si>
-    <t>ANEL</t>
-  </si>
-  <si>
-    <t>LAURA IVETTE</t>
-  </si>
-  <si>
-    <t>altamiranokaren999@gmail.com</t>
-  </si>
-  <si>
-    <t>isanga0805@gmail.com</t>
-  </si>
-  <si>
-    <t>arroyocitlalli@hotmail.com</t>
-  </si>
-  <si>
-    <t>guapotamichelle@gmail.com</t>
-  </si>
-  <si>
-    <t>Timy.caraza.cruz@gmail.com</t>
-  </si>
-  <si>
-    <t>danielcargz@gmail.com</t>
-  </si>
-  <si>
-    <t>arielcamarillo76@gmail.com</t>
-  </si>
-  <si>
-    <t>vcruzcansino@gmail.com</t>
-  </si>
-  <si>
-    <t>valeryangel26@gmail.com</t>
-  </si>
-  <si>
-    <t>stephaniegasca92@gmail.com</t>
-  </si>
-  <si>
-    <t>siaridanahygaliciapaz@gmail.com</t>
-  </si>
-  <si>
-    <t>aztequitatupapi@gmail.com</t>
-  </si>
-  <si>
-    <t>herrera12berth@gmail.com</t>
-  </si>
-  <si>
-    <t>alexapradoh@gmail.com</t>
-  </si>
-  <si>
-    <t>ariadnaramirez162@gmail.com</t>
-  </si>
-  <si>
-    <t>elianleyva14@gmail.com</t>
-  </si>
-  <si>
-    <t>nina.mmlm@gamil.com</t>
-  </si>
-  <si>
-    <t>1k3rd3lun4@gmail.com</t>
-  </si>
-  <si>
-    <t>santilop493@gmail.com</t>
-  </si>
-  <si>
-    <t>josemart041020@gmail.com</t>
-  </si>
-  <si>
-    <t>griselserrano11218@gmail.com</t>
-  </si>
-  <si>
-    <t>jesusenrique122004@gmail.com</t>
-  </si>
-  <si>
-    <t>cambelsaguilar@gmail.com</t>
-  </si>
-  <si>
-    <t>alejandranavarrorobles0503@gmail.com</t>
-  </si>
-  <si>
-    <t>marianaperezmorales17@gmail.com</t>
-  </si>
-  <si>
-    <t>marisolrs800@gmail.com</t>
-  </si>
-  <si>
-    <t>ramoszepedasamantha@gmail.com</t>
-  </si>
-  <si>
-    <t>arantzar33@gmail.com</t>
-  </si>
-  <si>
-    <t>rojas.2004.dulce15@gmail.com</t>
-  </si>
-  <si>
-    <t>santilu0505@gmail.com</t>
-  </si>
-  <si>
-    <t>ntorrescarrera@gmail.com</t>
-  </si>
-  <si>
-    <t>renicarrasco75@gmail.com</t>
-  </si>
-  <si>
-    <t>joselintorres79123@gmail.com</t>
-  </si>
-  <si>
-    <t>tabaniarenzano@gmail.com</t>
-  </si>
-  <si>
-    <t>faluivette03@gmail.com</t>
-  </si>
-  <si>
-    <t>2721222536</t>
-  </si>
-  <si>
-    <t>2721698901</t>
-  </si>
-  <si>
-    <t>2722821050</t>
-  </si>
-  <si>
-    <t>2721089340</t>
-  </si>
-  <si>
-    <t>2722960589</t>
-  </si>
-  <si>
-    <t>2721383983</t>
-  </si>
-  <si>
-    <t>2722468972</t>
-  </si>
-  <si>
-    <t>2721706496</t>
-  </si>
-  <si>
-    <t>2727843492</t>
-  </si>
-  <si>
-    <t>2721586212</t>
-  </si>
-  <si>
-    <t>2723354956</t>
-  </si>
-  <si>
-    <t>2722628012</t>
-  </si>
-  <si>
-    <t>2721350028</t>
-  </si>
-  <si>
-    <t>2721138149</t>
-  </si>
-  <si>
-    <t>2721578705</t>
-  </si>
-  <si>
-    <t>2722595581</t>
-  </si>
-  <si>
-    <t>2721179455</t>
-  </si>
-  <si>
-    <t>2722600861</t>
-  </si>
-  <si>
-    <t>2722805311</t>
-  </si>
-  <si>
-    <t>2721633478</t>
-  </si>
-  <si>
-    <t>2721966360</t>
-  </si>
-  <si>
-    <t>2725729386</t>
-  </si>
-  <si>
-    <t>2721207603</t>
-  </si>
-  <si>
-    <t>2721282076</t>
-  </si>
-  <si>
-    <t>2722426314</t>
-  </si>
-  <si>
-    <t>2721926504</t>
-  </si>
-  <si>
-    <t>2722337199</t>
-  </si>
-  <si>
-    <t>2722960143</t>
-  </si>
-  <si>
-    <t>2721413122</t>
-  </si>
-  <si>
-    <t>2722044505</t>
-  </si>
-  <si>
-    <t>2721315316</t>
-  </si>
-  <si>
-    <t>2721201026</t>
-  </si>
-  <si>
-    <t>2722293076</t>
-  </si>
-  <si>
-    <t>2722841219</t>
-  </si>
-  <si>
-    <t>2727213347</t>
-  </si>
-  <si>
-    <t>2721712859</t>
-  </si>
-  <si>
-    <t>2712753922</t>
-  </si>
-  <si>
-    <t>2721474215</t>
-  </si>
-  <si>
-    <t>2722174055</t>
-  </si>
-  <si>
-    <t>2726883799</t>
-  </si>
-  <si>
-    <t>2722356724</t>
-  </si>
-  <si>
-    <t>2722108990</t>
-  </si>
-  <si>
-    <t>2722110166</t>
-  </si>
-  <si>
-    <t>2721056621</t>
-  </si>
-  <si>
-    <t>2726880117</t>
-  </si>
-  <si>
-    <t>2727213395</t>
-  </si>
-  <si>
-    <t>2722456652</t>
-  </si>
-  <si>
-    <t>2722110160</t>
-  </si>
-  <si>
-    <t>2722894576</t>
-  </si>
-  <si>
-    <t>2722017247</t>
-  </si>
-  <si>
-    <t>2721712193</t>
-  </si>
-  <si>
-    <t>EVARISTO ALTAMIRANO DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>FELIPE ANTONIO REYES</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL ARROYO NAJERA</t>
-  </si>
-  <si>
-    <t>ESTANISLAO ALFONSO CASTRO</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL CARAZA CRUZ</t>
-  </si>
-  <si>
-    <t>FAUSTA RODRÍGUEZ GARCÍA</t>
-  </si>
-  <si>
-    <t>ARIEL CAMARILLO JAIMES</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL CRUZ SIGALA</t>
-  </si>
-  <si>
-    <t>RAYMUNDO FLORES VASQUEZ</t>
-  </si>
-  <si>
-    <t>ESTEBAN GASCA PEREZ</t>
-  </si>
-  <si>
-    <t>RUBEN GALICIA BAUTISTA</t>
-  </si>
-  <si>
-    <t>GONZALO GONZALEZ CASTRO</t>
-  </si>
-  <si>
-    <t>IVÁN HERRERA LUNA</t>
-  </si>
-  <si>
-    <t>CLAUDIA PRADO GARCÍA</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL HERRERA TREJO</t>
-  </si>
-  <si>
-    <t>EFRAÍN LEYVA RAMÍREZ</t>
-  </si>
-  <si>
-    <t>JUAN JOSÉ LÓPEZ CONTRERAS</t>
-  </si>
-  <si>
-    <t>AGUSTIN MARTINEZ CRISTOBAL</t>
-  </si>
-  <si>
-    <t>DANIEL MARTÍNEZ SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>FERNANDO JAIR MALDONADO GONZÁLEZ</t>
-  </si>
-  <si>
-    <t>ENRIQUE MIRAFUENTES TORRES</t>
-  </si>
-  <si>
-    <t>ILIANA AGUILAR MENA</t>
-  </si>
-  <si>
-    <t>LETICIA ROBLES SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>SERGIO PÉREZ HUERTA</t>
-  </si>
-  <si>
-    <t>ROSARIO JUAREZ SANCHEZ</t>
-  </si>
-  <si>
-    <t>SALVADOR RAMOS ZAVALA</t>
-  </si>
-  <si>
-    <t>ELISA REYES PÉREZ</t>
-  </si>
-  <si>
-    <t>EZEQUIEL ROJAS MEDINA</t>
-  </si>
-  <si>
-    <t>MARIO SANTIAGO MENDEZ</t>
-  </si>
-  <si>
-    <t>MARÍA DEL SOCORRO CARRERA HERNÁNDEZ</t>
-  </si>
-  <si>
-    <t>GERMAN TORRES ARIAS</t>
-  </si>
-  <si>
-    <t>IGNACIO MALAQUIAS TORRES CERONIO</t>
-  </si>
-  <si>
-    <t>ARMANDO VENTURA VERA</t>
-  </si>
-  <si>
-    <t>JESUS XOCUA CAMPOS</t>
-  </si>
-  <si>
-    <t>evaristo100680@gmail.com</t>
-  </si>
-  <si>
-    <t>anrefe74@hotmail.com</t>
-  </si>
-  <si>
-    <t>victor_arr97@hotmail.con</t>
-  </si>
-  <si>
-    <t>tanisalfonso8@gmail.com</t>
-  </si>
-  <si>
-    <t>johnny_cruz@hotmail.com</t>
-  </si>
-  <si>
-    <t>faufaurg@gmail.com</t>
-  </si>
-  <si>
-    <t>juanmcruzsigala@gmail.com</t>
-  </si>
-  <si>
-    <t>rayf0352@gmail.com</t>
-  </si>
-  <si>
-    <t>Ruben8405@gmail.com</t>
-  </si>
-  <si>
-    <t>gonzalo713100@gmail.com</t>
-  </si>
-  <si>
-    <t>clauxprado@gmail.com</t>
-  </si>
-  <si>
-    <t>marvic820225@gmail.com</t>
-  </si>
-  <si>
-    <t>Joselopcon2768@gmail.com</t>
-  </si>
-  <si>
-    <t>Santilop493@gmail.com</t>
-  </si>
-  <si>
-    <t>ferjair71@gmail.com</t>
-  </si>
-  <si>
-    <t>refriespe_786@hotmail.com</t>
-  </si>
-  <si>
-    <t>Cambelsaguilar@gmail.com</t>
-  </si>
-  <si>
-    <t>Perezhuertasergio4@gmail.com</t>
-  </si>
-  <si>
-    <t>samyzepeda15@gmail.com</t>
-  </si>
-  <si>
-    <t>elisareyesperez140@gmal.com</t>
-  </si>
-  <si>
-    <t>mario.san01@hotmail.com</t>
-  </si>
-  <si>
-    <t>Germantorres2504@gmail.com</t>
-  </si>
-  <si>
-    <t>nachitoeyr@gmail.com</t>
-  </si>
-  <si>
-    <t>xventa@hotmail.com</t>
-  </si>
-  <si>
-    <t>sky_ituns_@hotmail.com</t>
-  </si>
-  <si>
-    <t>2727823441</t>
-  </si>
-  <si>
-    <t>27229706655</t>
-  </si>
-  <si>
-    <t>2711481769</t>
-  </si>
-  <si>
-    <t>2721692982</t>
-  </si>
-  <si>
-    <t>2722255234</t>
-  </si>
-  <si>
-    <t>2722030880</t>
-  </si>
-  <si>
-    <t>2721356570</t>
-  </si>
-  <si>
-    <t>2721456231</t>
-  </si>
-  <si>
-    <t>2721644477</t>
-  </si>
-  <si>
-    <t>2721278597</t>
-  </si>
-  <si>
-    <t>2721389978</t>
-  </si>
-  <si>
-    <t>2721116261</t>
-  </si>
-  <si>
-    <t>2721289150</t>
-  </si>
-  <si>
-    <t>9711311117</t>
-  </si>
-  <si>
-    <t>2722956004</t>
-  </si>
-  <si>
-    <t>9921059452</t>
-  </si>
-  <si>
-    <t>2721397474</t>
-  </si>
-  <si>
-    <t>2721340853</t>
-  </si>
-  <si>
-    <t>9211798607</t>
-  </si>
-  <si>
-    <t>2721393961</t>
-  </si>
-  <si>
-    <t>2721821541</t>
-  </si>
-  <si>
-    <t>2721583583</t>
-  </si>
-  <si>
-    <t>2727053277</t>
-  </si>
-  <si>
-    <t>2721917182</t>
-  </si>
-  <si>
-    <t>5588003430</t>
-  </si>
-  <si>
-    <t>2721490103</t>
-  </si>
-  <si>
-    <t>2721386186</t>
-  </si>
-  <si>
-    <t>2721765023</t>
-  </si>
-  <si>
-    <t>2226611097</t>
-  </si>
-  <si>
-    <t>2721976523</t>
-  </si>
-  <si>
-    <t>2721587875</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CUEVAS</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>NAMIGTLE</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>URBANO</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>XILCAHUA</t>
-  </si>
-  <si>
-    <t>ATILANO</t>
-  </si>
-  <si>
-    <t>VILLALBA</t>
-  </si>
-  <si>
-    <t>ZAVALETA</t>
   </si>
   <si>
     <t>PIMENTEL</t>
@@ -5120,702 +4708,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="50.7109375" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2">
-        <v>20330051920260</v>
-      </c>
-      <c r="B2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D2" t="s">
-        <v>289</v>
-      </c>
-      <c r="E2" t="s">
-        <v>309</v>
-      </c>
-      <c r="F2" t="s">
-        <v>330</v>
-      </c>
-      <c r="G2" t="s">
-        <v>351</v>
-      </c>
-      <c r="H2" t="s">
-        <v>363</v>
-      </c>
-      <c r="I2" t="s">
-        <v>384</v>
-      </c>
-      <c r="J2" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3">
-        <v>20330051920261</v>
-      </c>
-      <c r="B3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C3" t="s">
-        <v>278</v>
-      </c>
-      <c r="D3" t="s">
-        <v>290</v>
-      </c>
-      <c r="E3" t="s">
-        <v>310</v>
-      </c>
-      <c r="F3" t="s">
-        <v>331</v>
-      </c>
-      <c r="G3" t="s">
-        <v>352</v>
-      </c>
-      <c r="H3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I3" t="s">
-        <v>385</v>
-      </c>
-      <c r="J3" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4">
-        <v>19330051920314</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D4" t="s">
-        <v>291</v>
-      </c>
-      <c r="E4" t="s">
-        <v>311</v>
-      </c>
-      <c r="F4" t="s">
-        <v>332</v>
-      </c>
-      <c r="G4" t="s">
-        <v>353</v>
-      </c>
-      <c r="H4" t="s">
-        <v>365</v>
-      </c>
-      <c r="I4" t="s">
-        <v>386</v>
-      </c>
-      <c r="J4" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5">
-        <v>20330051920262</v>
-      </c>
-      <c r="B5" t="s">
-        <v>266</v>
-      </c>
-      <c r="C5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D5" t="s">
-        <v>292</v>
-      </c>
-      <c r="E5" t="s">
-        <v>312</v>
-      </c>
-      <c r="F5" t="s">
-        <v>333</v>
-      </c>
-      <c r="G5" t="s">
-        <v>354</v>
-      </c>
-      <c r="H5" t="s">
-        <v>366</v>
-      </c>
-      <c r="I5" t="s">
-        <v>387</v>
-      </c>
-      <c r="J5" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6">
-        <v>20330051920264</v>
-      </c>
-      <c r="B6" t="s">
-        <v>267</v>
-      </c>
-      <c r="C6" t="s">
-        <v>280</v>
-      </c>
-      <c r="D6" t="s">
-        <v>293</v>
-      </c>
-      <c r="E6" t="s">
-        <v>313</v>
-      </c>
-      <c r="F6" t="s">
-        <v>334</v>
-      </c>
-      <c r="G6" t="s">
-        <v>334</v>
-      </c>
-      <c r="H6" t="s">
-        <v>367</v>
-      </c>
-      <c r="I6" t="s">
-        <v>388</v>
-      </c>
-      <c r="J6" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7">
-        <v>20330051920267</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>281</v>
-      </c>
-      <c r="D7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" t="s">
-        <v>314</v>
-      </c>
-      <c r="F7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G7" t="s">
-        <v>335</v>
-      </c>
-      <c r="H7" t="s">
-        <v>368</v>
-      </c>
-      <c r="I7" t="s">
-        <v>389</v>
-      </c>
-      <c r="J7" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8">
-        <v>20330051920268</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>294</v>
-      </c>
-      <c r="E8" t="s">
-        <v>315</v>
-      </c>
-      <c r="F8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G8" t="s">
-        <v>355</v>
-      </c>
-      <c r="H8" t="s">
-        <v>369</v>
-      </c>
-      <c r="I8" t="s">
-        <v>390</v>
-      </c>
-      <c r="J8" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9">
-        <v>20330051920269</v>
-      </c>
-      <c r="B9" t="s">
-        <v>268</v>
-      </c>
-      <c r="C9" t="s">
-        <v>282</v>
-      </c>
-      <c r="D9" t="s">
-        <v>295</v>
-      </c>
-      <c r="E9" t="s">
-        <v>316</v>
-      </c>
-      <c r="F9" t="s">
-        <v>337</v>
-      </c>
-      <c r="H9" t="s">
-        <v>370</v>
-      </c>
-      <c r="I9" t="s">
-        <v>391</v>
-      </c>
-      <c r="J9" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10">
-        <v>20330051920270</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" t="s">
-        <v>283</v>
-      </c>
-      <c r="D10" t="s">
-        <v>296</v>
-      </c>
-      <c r="E10" t="s">
-        <v>317</v>
-      </c>
-      <c r="F10" t="s">
-        <v>338</v>
-      </c>
-      <c r="G10" t="s">
-        <v>356</v>
-      </c>
-      <c r="H10" t="s">
-        <v>371</v>
-      </c>
-      <c r="I10" t="s">
-        <v>392</v>
-      </c>
-      <c r="J10" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11">
-        <v>20330051920271</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>284</v>
-      </c>
-      <c r="D11" t="s">
-        <v>297</v>
-      </c>
-      <c r="E11" t="s">
-        <v>318</v>
-      </c>
-      <c r="F11" t="s">
-        <v>339</v>
-      </c>
-      <c r="H11" t="s">
-        <v>372</v>
-      </c>
-      <c r="I11" t="s">
-        <v>393</v>
-      </c>
-      <c r="J11" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12">
-        <v>20330051920272</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" t="s">
-        <v>298</v>
-      </c>
-      <c r="E12" t="s">
-        <v>319</v>
-      </c>
-      <c r="F12" t="s">
-        <v>340</v>
-      </c>
-      <c r="H12" t="s">
-        <v>373</v>
-      </c>
-      <c r="I12" t="s">
-        <v>394</v>
-      </c>
-      <c r="J12" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13">
-        <v>19220030050208</v>
-      </c>
-      <c r="B13" t="s">
-        <v>269</v>
-      </c>
-      <c r="C13" t="s">
-        <v>285</v>
-      </c>
-      <c r="D13" t="s">
-        <v>299</v>
-      </c>
-      <c r="E13" t="s">
-        <v>320</v>
-      </c>
-      <c r="F13" t="s">
-        <v>341</v>
-      </c>
-      <c r="G13" t="s">
-        <v>357</v>
-      </c>
-      <c r="H13" t="s">
-        <v>374</v>
-      </c>
-      <c r="I13" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14">
-        <v>20330051920273</v>
-      </c>
-      <c r="B14" t="s">
-        <v>270</v>
-      </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" t="s">
-        <v>300</v>
-      </c>
-      <c r="E14" t="s">
-        <v>321</v>
-      </c>
-      <c r="F14" t="s">
-        <v>342</v>
-      </c>
-      <c r="G14" t="s">
-        <v>358</v>
-      </c>
-      <c r="H14" t="s">
-        <v>375</v>
-      </c>
-      <c r="I14" t="s">
-        <v>396</v>
-      </c>
-      <c r="J14" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15">
-        <v>20330051920274</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>301</v>
-      </c>
-      <c r="E15" t="s">
-        <v>322</v>
-      </c>
-      <c r="F15" t="s">
-        <v>343</v>
-      </c>
-      <c r="H15" t="s">
-        <v>376</v>
-      </c>
-      <c r="I15" t="s">
-        <v>397</v>
-      </c>
-      <c r="J15" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16">
-        <v>20330051920276</v>
-      </c>
-      <c r="B16" t="s">
-        <v>271</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" t="s">
-        <v>302</v>
-      </c>
-      <c r="E16" t="s">
-        <v>323</v>
-      </c>
-      <c r="F16" t="s">
-        <v>344</v>
-      </c>
-      <c r="G16" t="s">
-        <v>359</v>
-      </c>
-      <c r="H16" t="s">
-        <v>377</v>
-      </c>
-      <c r="I16" t="s">
-        <v>398</v>
-      </c>
-      <c r="J16" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17">
-        <v>19330051920238</v>
-      </c>
-      <c r="B17" t="s">
-        <v>272</v>
-      </c>
-      <c r="C17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" t="s">
-        <v>303</v>
-      </c>
-      <c r="E17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F17" t="s">
-        <v>345</v>
-      </c>
-      <c r="H17" t="s">
-        <v>378</v>
-      </c>
-      <c r="I17" t="s">
-        <v>324</v>
-      </c>
-      <c r="J17" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18">
-        <v>20330051920278</v>
-      </c>
-      <c r="B18" t="s">
-        <v>273</v>
-      </c>
-      <c r="C18" t="s">
-        <v>286</v>
-      </c>
-      <c r="D18" t="s">
-        <v>304</v>
-      </c>
-      <c r="E18" t="s">
-        <v>325</v>
-      </c>
-      <c r="F18" t="s">
-        <v>346</v>
-      </c>
-      <c r="G18" t="s">
-        <v>360</v>
-      </c>
-      <c r="H18" t="s">
-        <v>379</v>
-      </c>
-      <c r="I18" t="s">
-        <v>399</v>
-      </c>
-      <c r="J18" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19">
-        <v>20330051920279</v>
-      </c>
-      <c r="B19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" t="s">
-        <v>287</v>
-      </c>
-      <c r="D19" t="s">
-        <v>305</v>
-      </c>
-      <c r="E19" t="s">
-        <v>326</v>
-      </c>
-      <c r="F19" t="s">
-        <v>347</v>
-      </c>
-      <c r="G19" t="s">
-        <v>361</v>
-      </c>
-      <c r="H19" t="s">
-        <v>380</v>
-      </c>
-      <c r="I19" t="s">
-        <v>400</v>
-      </c>
-      <c r="J19" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20">
-        <v>20330051920281</v>
-      </c>
-      <c r="B20" t="s">
-        <v>274</v>
-      </c>
-      <c r="C20" t="s">
-        <v>288</v>
-      </c>
-      <c r="D20" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" t="s">
-        <v>327</v>
-      </c>
-      <c r="F20" t="s">
-        <v>348</v>
-      </c>
-      <c r="G20" t="s">
-        <v>348</v>
-      </c>
-      <c r="H20" t="s">
-        <v>381</v>
-      </c>
-      <c r="I20" t="s">
-        <v>401</v>
-      </c>
-      <c r="J20" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21">
-        <v>20330051920282</v>
-      </c>
-      <c r="B21" t="s">
-        <v>275</v>
-      </c>
-      <c r="C21" t="s">
-        <v>273</v>
-      </c>
-      <c r="D21" t="s">
-        <v>307</v>
-      </c>
-      <c r="E21" t="s">
-        <v>328</v>
-      </c>
-      <c r="F21" t="s">
-        <v>349</v>
-      </c>
-      <c r="H21" t="s">
-        <v>382</v>
-      </c>
-      <c r="I21" t="s">
-        <v>402</v>
-      </c>
-      <c r="J21" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22">
-        <v>19330051920425</v>
-      </c>
-      <c r="B22" t="s">
-        <v>276</v>
-      </c>
-      <c r="C22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" t="s">
-        <v>308</v>
-      </c>
-      <c r="E22" t="s">
-        <v>329</v>
-      </c>
-      <c r="F22" t="s">
-        <v>350</v>
-      </c>
-      <c r="G22" t="s">
-        <v>362</v>
-      </c>
-      <c r="H22" t="s">
-        <v>383</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5865,25 +4757,25 @@
         <v>20330051920317</v>
       </c>
       <c r="B2" t="s">
-        <v>421</v>
+        <v>264</v>
       </c>
       <c r="C2" t="s">
-        <v>435</v>
+        <v>279</v>
       </c>
       <c r="D2" t="s">
-        <v>447</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s">
-        <v>469</v>
+        <v>315</v>
       </c>
       <c r="H2" t="s">
-        <v>522</v>
+        <v>368</v>
       </c>
       <c r="I2" t="s">
-        <v>544</v>
+        <v>390</v>
       </c>
       <c r="J2" t="s">
-        <v>562</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5891,31 +4783,31 @@
         <v>20330051920318</v>
       </c>
       <c r="B3" t="s">
-        <v>422</v>
+        <v>265</v>
       </c>
       <c r="C3" t="s">
-        <v>436</v>
+        <v>280</v>
       </c>
       <c r="D3" t="s">
-        <v>448</v>
+        <v>294</v>
       </c>
       <c r="E3" t="s">
-        <v>470</v>
+        <v>316</v>
       </c>
       <c r="F3" t="s">
-        <v>491</v>
+        <v>337</v>
       </c>
       <c r="G3" t="s">
-        <v>512</v>
+        <v>358</v>
       </c>
       <c r="H3" t="s">
-        <v>523</v>
+        <v>369</v>
       </c>
       <c r="I3" t="s">
-        <v>545</v>
+        <v>391</v>
       </c>
       <c r="J3" t="s">
-        <v>563</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5923,28 +4815,28 @@
         <v>20330050470026</v>
       </c>
       <c r="B4" t="s">
-        <v>423</v>
+        <v>266</v>
       </c>
       <c r="C4" t="s">
-        <v>437</v>
+        <v>281</v>
       </c>
       <c r="D4" t="s">
-        <v>449</v>
+        <v>295</v>
       </c>
       <c r="E4" t="s">
-        <v>471</v>
+        <v>317</v>
       </c>
       <c r="F4" t="s">
-        <v>492</v>
+        <v>338</v>
       </c>
       <c r="H4" t="s">
-        <v>524</v>
+        <v>370</v>
       </c>
       <c r="I4" t="s">
-        <v>546</v>
+        <v>392</v>
       </c>
       <c r="J4" t="s">
-        <v>564</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5952,28 +4844,28 @@
         <v>20330051920320</v>
       </c>
       <c r="B5" t="s">
-        <v>424</v>
+        <v>267</v>
       </c>
       <c r="C5" t="s">
-        <v>438</v>
+        <v>282</v>
       </c>
       <c r="D5" t="s">
-        <v>450</v>
+        <v>296</v>
       </c>
       <c r="E5" t="s">
-        <v>472</v>
+        <v>318</v>
       </c>
       <c r="F5" t="s">
-        <v>493</v>
+        <v>339</v>
       </c>
       <c r="H5" t="s">
-        <v>525</v>
+        <v>371</v>
       </c>
       <c r="I5" t="s">
-        <v>547</v>
+        <v>393</v>
       </c>
       <c r="J5" t="s">
-        <v>565</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -5981,25 +4873,25 @@
         <v>20330051920321</v>
       </c>
       <c r="B6" t="s">
-        <v>425</v>
+        <v>268</v>
       </c>
       <c r="C6" t="s">
-        <v>439</v>
+        <v>283</v>
       </c>
       <c r="D6" t="s">
-        <v>451</v>
+        <v>297</v>
       </c>
       <c r="E6" t="s">
-        <v>473</v>
+        <v>319</v>
       </c>
       <c r="F6" t="s">
-        <v>494</v>
+        <v>340</v>
       </c>
       <c r="G6" t="s">
-        <v>494</v>
+        <v>340</v>
       </c>
       <c r="H6" t="s">
-        <v>526</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6013,25 +4905,25 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>452</v>
+        <v>298</v>
       </c>
       <c r="E7" t="s">
-        <v>474</v>
+        <v>320</v>
       </c>
       <c r="F7" t="s">
-        <v>495</v>
+        <v>341</v>
       </c>
       <c r="G7" t="s">
-        <v>513</v>
+        <v>359</v>
       </c>
       <c r="H7" t="s">
-        <v>527</v>
+        <v>373</v>
       </c>
       <c r="I7" t="s">
-        <v>548</v>
+        <v>394</v>
       </c>
       <c r="J7" t="s">
-        <v>566</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6042,28 +4934,28 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>440</v>
+        <v>284</v>
       </c>
       <c r="D8" t="s">
-        <v>453</v>
+        <v>299</v>
       </c>
       <c r="E8" t="s">
-        <v>475</v>
+        <v>321</v>
       </c>
       <c r="F8" t="s">
-        <v>496</v>
+        <v>342</v>
       </c>
       <c r="G8" t="s">
-        <v>514</v>
+        <v>360</v>
       </c>
       <c r="H8" t="s">
-        <v>528</v>
+        <v>374</v>
       </c>
       <c r="I8" t="s">
-        <v>549</v>
+        <v>395</v>
       </c>
       <c r="J8" t="s">
-        <v>567</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6071,28 +4963,28 @@
         <v>20330051920380</v>
       </c>
       <c r="B9" t="s">
-        <v>426</v>
+        <v>269</v>
       </c>
       <c r="C9" t="s">
-        <v>441</v>
+        <v>285</v>
       </c>
       <c r="D9" t="s">
-        <v>454</v>
+        <v>300</v>
       </c>
       <c r="E9" t="s">
-        <v>476</v>
+        <v>322</v>
       </c>
       <c r="F9" t="s">
-        <v>497</v>
+        <v>343</v>
       </c>
       <c r="H9" t="s">
-        <v>529</v>
+        <v>375</v>
       </c>
       <c r="I9" t="s">
-        <v>550</v>
+        <v>396</v>
       </c>
       <c r="J9" t="s">
-        <v>568</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6106,25 +4998,25 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>455</v>
+        <v>301</v>
       </c>
       <c r="E10" t="s">
-        <v>477</v>
+        <v>323</v>
       </c>
       <c r="F10" t="s">
-        <v>498</v>
+        <v>344</v>
       </c>
       <c r="G10" t="s">
-        <v>515</v>
+        <v>361</v>
       </c>
       <c r="H10" t="s">
-        <v>530</v>
+        <v>376</v>
       </c>
       <c r="I10" t="s">
-        <v>551</v>
+        <v>397</v>
       </c>
       <c r="J10" t="s">
-        <v>569</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6135,28 +5027,28 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>442</v>
+        <v>286</v>
       </c>
       <c r="D11" t="s">
-        <v>456</v>
+        <v>302</v>
       </c>
       <c r="E11" t="s">
-        <v>478</v>
+        <v>324</v>
       </c>
       <c r="F11" t="s">
-        <v>499</v>
+        <v>345</v>
       </c>
       <c r="G11" t="s">
-        <v>516</v>
+        <v>362</v>
       </c>
       <c r="H11" t="s">
-        <v>531</v>
+        <v>377</v>
       </c>
       <c r="I11" t="s">
-        <v>552</v>
+        <v>398</v>
       </c>
       <c r="J11" t="s">
-        <v>570</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6164,31 +5056,31 @@
         <v>20330051920397</v>
       </c>
       <c r="B12" t="s">
-        <v>427</v>
+        <v>270</v>
       </c>
       <c r="C12" t="s">
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>457</v>
+        <v>303</v>
       </c>
       <c r="E12" t="s">
-        <v>479</v>
+        <v>325</v>
       </c>
       <c r="F12" t="s">
-        <v>500</v>
+        <v>346</v>
       </c>
       <c r="G12" t="s">
-        <v>517</v>
+        <v>363</v>
       </c>
       <c r="H12" t="s">
-        <v>532</v>
+        <v>378</v>
       </c>
       <c r="I12" t="s">
-        <v>479</v>
+        <v>325</v>
       </c>
       <c r="J12" t="s">
-        <v>571</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6196,28 +5088,28 @@
         <v>20330051920326</v>
       </c>
       <c r="B13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>458</v>
+        <v>304</v>
       </c>
       <c r="E13" t="s">
-        <v>480</v>
+        <v>326</v>
       </c>
       <c r="F13" t="s">
-        <v>501</v>
+        <v>347</v>
       </c>
       <c r="H13" t="s">
-        <v>533</v>
+        <v>379</v>
       </c>
       <c r="I13" t="s">
-        <v>553</v>
+        <v>399</v>
       </c>
       <c r="J13" t="s">
-        <v>572</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6225,28 +5117,28 @@
         <v>20330051920327</v>
       </c>
       <c r="B14" t="s">
-        <v>428</v>
+        <v>272</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>459</v>
+        <v>305</v>
       </c>
       <c r="E14" t="s">
-        <v>481</v>
+        <v>327</v>
       </c>
       <c r="F14" t="s">
-        <v>502</v>
+        <v>348</v>
       </c>
       <c r="H14" t="s">
-        <v>534</v>
+        <v>380</v>
       </c>
       <c r="I14" t="s">
-        <v>554</v>
+        <v>400</v>
       </c>
       <c r="J14" t="s">
-        <v>573</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6254,31 +5146,31 @@
         <v>20330051920328</v>
       </c>
       <c r="B15" t="s">
-        <v>429</v>
+        <v>273</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>460</v>
+        <v>306</v>
       </c>
       <c r="E15" t="s">
-        <v>482</v>
+        <v>328</v>
       </c>
       <c r="F15" t="s">
-        <v>503</v>
+        <v>349</v>
       </c>
       <c r="G15" t="s">
-        <v>503</v>
+        <v>349</v>
       </c>
       <c r="H15" t="s">
-        <v>535</v>
+        <v>381</v>
       </c>
       <c r="I15" t="s">
-        <v>555</v>
+        <v>401</v>
       </c>
       <c r="J15" t="s">
-        <v>574</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6286,31 +5178,31 @@
         <v>20330051920396</v>
       </c>
       <c r="B16" t="s">
-        <v>430</v>
+        <v>274</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>461</v>
+        <v>307</v>
       </c>
       <c r="E16" t="s">
-        <v>483</v>
+        <v>329</v>
       </c>
       <c r="F16" t="s">
-        <v>504</v>
+        <v>350</v>
       </c>
       <c r="G16" t="s">
-        <v>504</v>
+        <v>350</v>
       </c>
       <c r="H16" t="s">
-        <v>536</v>
+        <v>382</v>
       </c>
       <c r="I16" t="s">
-        <v>556</v>
+        <v>402</v>
       </c>
       <c r="J16" t="s">
-        <v>575</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -6318,31 +5210,31 @@
         <v>20330051920329</v>
       </c>
       <c r="B17" t="s">
-        <v>431</v>
+        <v>275</v>
       </c>
       <c r="C17" t="s">
-        <v>443</v>
+        <v>287</v>
       </c>
       <c r="D17" t="s">
-        <v>462</v>
+        <v>308</v>
       </c>
       <c r="E17" t="s">
-        <v>484</v>
+        <v>330</v>
       </c>
       <c r="F17" t="s">
-        <v>505</v>
+        <v>351</v>
       </c>
       <c r="G17" t="s">
-        <v>518</v>
+        <v>364</v>
       </c>
       <c r="H17" t="s">
-        <v>537</v>
+        <v>383</v>
       </c>
       <c r="I17" t="s">
-        <v>557</v>
+        <v>403</v>
       </c>
       <c r="J17" t="s">
-        <v>576</v>
+        <v>422</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6350,28 +5242,28 @@
         <v>20330051920330</v>
       </c>
       <c r="B18" t="s">
-        <v>432</v>
+        <v>276</v>
       </c>
       <c r="C18" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D18" t="s">
-        <v>463</v>
+        <v>309</v>
       </c>
       <c r="E18" t="s">
-        <v>485</v>
+        <v>331</v>
       </c>
       <c r="F18" t="s">
-        <v>506</v>
+        <v>352</v>
       </c>
       <c r="G18" t="s">
-        <v>519</v>
+        <v>365</v>
       </c>
       <c r="H18" t="s">
-        <v>538</v>
+        <v>384</v>
       </c>
       <c r="J18" t="s">
-        <v>577</v>
+        <v>423</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6382,25 +5274,25 @@
         <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>444</v>
+        <v>289</v>
       </c>
       <c r="D19" t="s">
-        <v>464</v>
+        <v>310</v>
       </c>
       <c r="E19" t="s">
-        <v>486</v>
+        <v>332</v>
       </c>
       <c r="F19" t="s">
-        <v>507</v>
+        <v>353</v>
       </c>
       <c r="H19" t="s">
-        <v>539</v>
+        <v>385</v>
       </c>
       <c r="I19" t="s">
-        <v>558</v>
+        <v>404</v>
       </c>
       <c r="J19" t="s">
-        <v>578</v>
+        <v>424</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -6411,28 +5303,28 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="D20" t="s">
-        <v>465</v>
+        <v>311</v>
       </c>
       <c r="E20" t="s">
-        <v>487</v>
+        <v>333</v>
       </c>
       <c r="F20" t="s">
-        <v>508</v>
+        <v>354</v>
       </c>
       <c r="G20" t="s">
-        <v>520</v>
+        <v>366</v>
       </c>
       <c r="H20" t="s">
-        <v>540</v>
+        <v>386</v>
       </c>
       <c r="I20" t="s">
-        <v>559</v>
+        <v>405</v>
       </c>
       <c r="J20" t="s">
-        <v>579</v>
+        <v>425</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6443,28 +5335,28 @@
         <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>445</v>
+        <v>291</v>
       </c>
       <c r="D21" t="s">
-        <v>466</v>
+        <v>312</v>
       </c>
       <c r="E21" t="s">
-        <v>488</v>
+        <v>334</v>
       </c>
       <c r="F21" t="s">
-        <v>509</v>
+        <v>355</v>
       </c>
       <c r="G21" t="s">
-        <v>521</v>
+        <v>367</v>
       </c>
       <c r="H21" t="s">
-        <v>541</v>
+        <v>387</v>
       </c>
       <c r="I21" t="s">
-        <v>560</v>
+        <v>406</v>
       </c>
       <c r="J21" t="s">
-        <v>580</v>
+        <v>426</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -6472,31 +5364,31 @@
         <v>20330051920334</v>
       </c>
       <c r="B22" t="s">
-        <v>433</v>
+        <v>277</v>
       </c>
       <c r="C22" t="s">
-        <v>439</v>
+        <v>283</v>
       </c>
       <c r="D22" t="s">
-        <v>467</v>
+        <v>313</v>
       </c>
       <c r="E22" t="s">
-        <v>489</v>
+        <v>335</v>
       </c>
       <c r="F22" t="s">
-        <v>510</v>
+        <v>356</v>
       </c>
       <c r="G22" t="s">
-        <v>510</v>
+        <v>356</v>
       </c>
       <c r="H22" t="s">
-        <v>542</v>
+        <v>388</v>
       </c>
       <c r="I22" t="s">
-        <v>489</v>
+        <v>335</v>
       </c>
       <c r="J22" t="s">
-        <v>581</v>
+        <v>427</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6504,28 +5396,28 @@
         <v>20330051920335</v>
       </c>
       <c r="B23" t="s">
-        <v>434</v>
+        <v>278</v>
       </c>
       <c r="C23" t="s">
-        <v>446</v>
+        <v>292</v>
       </c>
       <c r="D23" t="s">
-        <v>468</v>
+        <v>314</v>
       </c>
       <c r="E23" t="s">
-        <v>490</v>
+        <v>336</v>
       </c>
       <c r="F23" t="s">
-        <v>511</v>
+        <v>357</v>
       </c>
       <c r="H23" t="s">
-        <v>543</v>
+        <v>389</v>
       </c>
       <c r="I23" t="s">
-        <v>561</v>
+        <v>407</v>
       </c>
       <c r="J23" t="s">
-        <v>582</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -6533,7 +5425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J33"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6584,31 +5476,31 @@
         <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
-        <v>583</v>
+        <v>429</v>
       </c>
       <c r="C2" t="s">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="D2" t="s">
-        <v>612</v>
+        <v>462</v>
       </c>
       <c r="E2" t="s">
-        <v>643</v>
+        <v>493</v>
       </c>
       <c r="F2" t="s">
-        <v>675</v>
+        <v>525</v>
       </c>
       <c r="G2" t="s">
-        <v>707</v>
+        <v>557</v>
       </c>
       <c r="H2" t="s">
-        <v>722</v>
+        <v>572</v>
       </c>
       <c r="I2" t="s">
-        <v>754</v>
+        <v>604</v>
       </c>
       <c r="J2" t="s">
-        <v>778</v>
+        <v>628</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6616,28 +5508,28 @@
         <v>20330051920040</v>
       </c>
       <c r="B3" t="s">
-        <v>584</v>
+        <v>430</v>
       </c>
       <c r="C3" t="s">
-        <v>601</v>
+        <v>451</v>
       </c>
       <c r="D3" t="s">
-        <v>613</v>
+        <v>463</v>
       </c>
       <c r="E3" t="s">
-        <v>644</v>
+        <v>494</v>
       </c>
       <c r="F3" t="s">
-        <v>676</v>
+        <v>526</v>
       </c>
       <c r="G3" t="s">
-        <v>708</v>
+        <v>558</v>
       </c>
       <c r="H3" t="s">
-        <v>723</v>
+        <v>573</v>
       </c>
       <c r="J3" t="s">
-        <v>779</v>
+        <v>629</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6645,28 +5537,28 @@
         <v>20330051920042</v>
       </c>
       <c r="B4" t="s">
-        <v>585</v>
+        <v>431</v>
       </c>
       <c r="C4" t="s">
         <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>614</v>
+        <v>464</v>
       </c>
       <c r="E4" t="s">
-        <v>645</v>
+        <v>495</v>
       </c>
       <c r="F4" t="s">
-        <v>677</v>
+        <v>527</v>
       </c>
       <c r="H4" t="s">
-        <v>724</v>
+        <v>574</v>
       </c>
       <c r="I4" t="s">
-        <v>755</v>
+        <v>605</v>
       </c>
       <c r="J4" t="s">
-        <v>780</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6674,31 +5566,31 @@
         <v>20330051920043</v>
       </c>
       <c r="B5" t="s">
-        <v>422</v>
+        <v>265</v>
       </c>
       <c r="C5" t="s">
-        <v>602</v>
+        <v>452</v>
       </c>
       <c r="D5" t="s">
-        <v>615</v>
+        <v>465</v>
       </c>
       <c r="E5" t="s">
-        <v>646</v>
+        <v>496</v>
       </c>
       <c r="F5" t="s">
-        <v>678</v>
+        <v>528</v>
       </c>
       <c r="G5" t="s">
-        <v>709</v>
+        <v>559</v>
       </c>
       <c r="H5" t="s">
-        <v>725</v>
+        <v>575</v>
       </c>
       <c r="I5" t="s">
-        <v>756</v>
+        <v>606</v>
       </c>
       <c r="J5" t="s">
-        <v>781</v>
+        <v>631</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6706,31 +5598,31 @@
         <v>20330051920044</v>
       </c>
       <c r="B6" t="s">
-        <v>586</v>
+        <v>432</v>
       </c>
       <c r="C6" t="s">
-        <v>603</v>
+        <v>453</v>
       </c>
       <c r="D6" t="s">
-        <v>616</v>
+        <v>466</v>
       </c>
       <c r="E6" t="s">
-        <v>647</v>
+        <v>497</v>
       </c>
       <c r="F6" t="s">
-        <v>679</v>
+        <v>529</v>
       </c>
       <c r="G6" t="s">
-        <v>710</v>
+        <v>560</v>
       </c>
       <c r="H6" t="s">
-        <v>726</v>
+        <v>576</v>
       </c>
       <c r="I6" t="s">
-        <v>757</v>
+        <v>607</v>
       </c>
       <c r="J6" t="s">
-        <v>710</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6738,31 +5630,31 @@
         <v>20330051920045</v>
       </c>
       <c r="B7" t="s">
-        <v>587</v>
+        <v>433</v>
       </c>
       <c r="C7" t="s">
         <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>617</v>
+        <v>467</v>
       </c>
       <c r="E7" t="s">
-        <v>648</v>
+        <v>498</v>
       </c>
       <c r="F7" t="s">
-        <v>680</v>
+        <v>530</v>
       </c>
       <c r="G7" t="s">
-        <v>711</v>
+        <v>561</v>
       </c>
       <c r="H7" t="s">
-        <v>727</v>
+        <v>577</v>
       </c>
       <c r="I7" t="s">
-        <v>758</v>
+        <v>608</v>
       </c>
       <c r="J7" t="s">
-        <v>782</v>
+        <v>632</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6770,31 +5662,31 @@
         <v>20330051920046</v>
       </c>
       <c r="B8" t="s">
-        <v>588</v>
+        <v>434</v>
       </c>
       <c r="C8" t="s">
-        <v>604</v>
+        <v>454</v>
       </c>
       <c r="D8" t="s">
-        <v>618</v>
+        <v>468</v>
       </c>
       <c r="E8" t="s">
-        <v>649</v>
+        <v>499</v>
       </c>
       <c r="F8" t="s">
-        <v>681</v>
+        <v>531</v>
       </c>
       <c r="G8" t="s">
-        <v>681</v>
+        <v>531</v>
       </c>
       <c r="H8" t="s">
-        <v>728</v>
+        <v>578</v>
       </c>
       <c r="I8" t="s">
-        <v>759</v>
+        <v>609</v>
       </c>
       <c r="J8" t="s">
-        <v>783</v>
+        <v>633</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6802,31 +5694,31 @@
         <v>20330051920048</v>
       </c>
       <c r="B9" t="s">
-        <v>589</v>
+        <v>435</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>619</v>
+        <v>469</v>
       </c>
       <c r="E9" t="s">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="F9" t="s">
-        <v>682</v>
+        <v>532</v>
       </c>
       <c r="G9" t="s">
-        <v>682</v>
+        <v>532</v>
       </c>
       <c r="H9" t="s">
-        <v>729</v>
+        <v>579</v>
       </c>
       <c r="I9" t="s">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="J9" t="s">
-        <v>784</v>
+        <v>634</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6834,28 +5726,28 @@
         <v>20330051920050</v>
       </c>
       <c r="B10" t="s">
-        <v>590</v>
+        <v>436</v>
       </c>
       <c r="C10" t="s">
-        <v>594</v>
+        <v>441</v>
       </c>
       <c r="D10" t="s">
-        <v>620</v>
+        <v>470</v>
       </c>
       <c r="E10" t="s">
-        <v>651</v>
+        <v>501</v>
       </c>
       <c r="F10" t="s">
-        <v>683</v>
+        <v>533</v>
       </c>
       <c r="H10" t="s">
-        <v>730</v>
+        <v>580</v>
       </c>
       <c r="I10" t="s">
-        <v>760</v>
+        <v>610</v>
       </c>
       <c r="J10" t="s">
-        <v>785</v>
+        <v>635</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6863,31 +5755,31 @@
         <v>20330051920051</v>
       </c>
       <c r="B11" t="s">
-        <v>591</v>
+        <v>437</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>618</v>
+        <v>468</v>
       </c>
       <c r="E11" t="s">
-        <v>652</v>
+        <v>502</v>
       </c>
       <c r="F11" t="s">
-        <v>684</v>
+        <v>534</v>
       </c>
       <c r="G11" t="s">
-        <v>712</v>
+        <v>562</v>
       </c>
       <c r="H11" t="s">
-        <v>731</v>
+        <v>581</v>
       </c>
       <c r="I11" t="s">
-        <v>652</v>
+        <v>502</v>
       </c>
       <c r="J11" t="s">
-        <v>786</v>
+        <v>636</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6895,28 +5787,28 @@
         <v>20330051920365</v>
       </c>
       <c r="B12" t="s">
-        <v>283</v>
+        <v>438</v>
       </c>
       <c r="C12" t="s">
-        <v>434</v>
+        <v>278</v>
       </c>
       <c r="D12" t="s">
-        <v>621</v>
+        <v>471</v>
       </c>
       <c r="E12" t="s">
-        <v>653</v>
+        <v>503</v>
       </c>
       <c r="F12" t="s">
-        <v>685</v>
+        <v>535</v>
       </c>
       <c r="H12" t="s">
-        <v>732</v>
+        <v>582</v>
       </c>
       <c r="I12" t="s">
-        <v>761</v>
+        <v>611</v>
       </c>
       <c r="J12" t="s">
-        <v>787</v>
+        <v>637</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6927,25 +5819,25 @@
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>605</v>
+        <v>455</v>
       </c>
       <c r="D13" t="s">
-        <v>622</v>
+        <v>472</v>
       </c>
       <c r="E13" t="s">
-        <v>654</v>
+        <v>504</v>
       </c>
       <c r="F13" t="s">
-        <v>686</v>
+        <v>536</v>
       </c>
       <c r="H13" t="s">
-        <v>733</v>
+        <v>583</v>
       </c>
       <c r="I13" t="s">
-        <v>654</v>
+        <v>504</v>
       </c>
       <c r="J13" t="s">
-        <v>788</v>
+        <v>638</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6959,25 +5851,25 @@
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>623</v>
+        <v>473</v>
       </c>
       <c r="E14" t="s">
-        <v>655</v>
+        <v>505</v>
       </c>
       <c r="F14" t="s">
-        <v>687</v>
+        <v>537</v>
       </c>
       <c r="G14" t="s">
-        <v>709</v>
+        <v>559</v>
       </c>
       <c r="H14" t="s">
-        <v>734</v>
+        <v>584</v>
       </c>
       <c r="I14" t="s">
-        <v>762</v>
+        <v>612</v>
       </c>
       <c r="J14" t="s">
-        <v>789</v>
+        <v>639</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6991,25 +5883,25 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>624</v>
+        <v>474</v>
       </c>
       <c r="E15" t="s">
-        <v>656</v>
+        <v>506</v>
       </c>
       <c r="F15" t="s">
-        <v>688</v>
+        <v>538</v>
       </c>
       <c r="G15" t="s">
-        <v>688</v>
+        <v>538</v>
       </c>
       <c r="H15" t="s">
-        <v>735</v>
+        <v>585</v>
       </c>
       <c r="I15" t="s">
-        <v>763</v>
+        <v>613</v>
       </c>
       <c r="J15" t="s">
-        <v>790</v>
+        <v>640</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -7017,31 +5909,31 @@
         <v>20330051920056</v>
       </c>
       <c r="B16" t="s">
-        <v>592</v>
+        <v>439</v>
       </c>
       <c r="C16" t="s">
         <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>625</v>
+        <v>475</v>
       </c>
       <c r="E16" t="s">
-        <v>657</v>
+        <v>507</v>
       </c>
       <c r="F16" t="s">
-        <v>689</v>
+        <v>539</v>
       </c>
       <c r="G16" t="s">
-        <v>713</v>
+        <v>563</v>
       </c>
       <c r="H16" t="s">
-        <v>736</v>
+        <v>586</v>
       </c>
       <c r="I16" t="s">
-        <v>764</v>
+        <v>614</v>
       </c>
       <c r="J16" t="s">
-        <v>791</v>
+        <v>641</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -7052,28 +5944,28 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>606</v>
+        <v>456</v>
       </c>
       <c r="D17" t="s">
-        <v>626</v>
+        <v>476</v>
       </c>
       <c r="E17" t="s">
-        <v>658</v>
+        <v>508</v>
       </c>
       <c r="F17" t="s">
-        <v>690</v>
+        <v>540</v>
       </c>
       <c r="G17" t="s">
-        <v>714</v>
+        <v>564</v>
       </c>
       <c r="H17" t="s">
-        <v>737</v>
+        <v>587</v>
       </c>
       <c r="I17" t="s">
-        <v>765</v>
+        <v>615</v>
       </c>
       <c r="J17" t="s">
-        <v>792</v>
+        <v>642</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -7081,25 +5973,25 @@
         <v>20330051920095</v>
       </c>
       <c r="B18" t="s">
-        <v>593</v>
+        <v>440</v>
       </c>
       <c r="C18" t="s">
-        <v>592</v>
+        <v>439</v>
       </c>
       <c r="D18" t="s">
-        <v>627</v>
+        <v>477</v>
       </c>
       <c r="E18" t="s">
-        <v>659</v>
+        <v>509</v>
       </c>
       <c r="F18" t="s">
-        <v>691</v>
+        <v>541</v>
       </c>
       <c r="H18" t="s">
-        <v>738</v>
+        <v>588</v>
       </c>
       <c r="J18" t="s">
-        <v>793</v>
+        <v>643</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -7110,28 +6002,28 @@
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>607</v>
+        <v>457</v>
       </c>
       <c r="D19" t="s">
-        <v>628</v>
+        <v>478</v>
       </c>
       <c r="E19" t="s">
-        <v>660</v>
+        <v>510</v>
       </c>
       <c r="F19" t="s">
-        <v>692</v>
+        <v>542</v>
       </c>
       <c r="G19" t="s">
-        <v>692</v>
+        <v>542</v>
       </c>
       <c r="H19" t="s">
-        <v>739</v>
+        <v>589</v>
       </c>
       <c r="I19" t="s">
-        <v>766</v>
+        <v>616</v>
       </c>
       <c r="J19" t="s">
-        <v>794</v>
+        <v>644</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -7139,31 +6031,31 @@
         <v>20330051920097</v>
       </c>
       <c r="B20" t="s">
-        <v>594</v>
+        <v>441</v>
       </c>
       <c r="C20" t="s">
-        <v>608</v>
+        <v>458</v>
       </c>
       <c r="D20" t="s">
-        <v>629</v>
+        <v>479</v>
       </c>
       <c r="E20" t="s">
-        <v>661</v>
+        <v>511</v>
       </c>
       <c r="F20" t="s">
-        <v>693</v>
+        <v>543</v>
       </c>
       <c r="G20" t="s">
-        <v>693</v>
+        <v>543</v>
       </c>
       <c r="H20" t="s">
-        <v>740</v>
+        <v>590</v>
       </c>
       <c r="I20" t="s">
-        <v>767</v>
+        <v>617</v>
       </c>
       <c r="J20" t="s">
-        <v>795</v>
+        <v>645</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7171,28 +6063,28 @@
         <v>20330051920099</v>
       </c>
       <c r="B21" t="s">
-        <v>595</v>
+        <v>442</v>
       </c>
       <c r="D21" t="s">
-        <v>630</v>
+        <v>480</v>
       </c>
       <c r="E21" t="s">
-        <v>662</v>
+        <v>512</v>
       </c>
       <c r="F21" t="s">
-        <v>694</v>
+        <v>544</v>
       </c>
       <c r="G21" t="s">
-        <v>715</v>
+        <v>565</v>
       </c>
       <c r="H21" t="s">
-        <v>741</v>
+        <v>591</v>
       </c>
       <c r="I21" t="s">
-        <v>768</v>
+        <v>618</v>
       </c>
       <c r="J21" t="s">
-        <v>796</v>
+        <v>646</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7200,28 +6092,28 @@
         <v>20330051920366</v>
       </c>
       <c r="B22" t="s">
-        <v>431</v>
+        <v>275</v>
       </c>
       <c r="C22" t="s">
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>631</v>
+        <v>481</v>
       </c>
       <c r="E22" t="s">
-        <v>663</v>
+        <v>513</v>
       </c>
       <c r="F22" t="s">
-        <v>695</v>
+        <v>545</v>
       </c>
       <c r="H22" t="s">
-        <v>742</v>
+        <v>592</v>
       </c>
       <c r="I22" t="s">
-        <v>769</v>
+        <v>619</v>
       </c>
       <c r="J22" t="s">
-        <v>696</v>
+        <v>546</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -7229,31 +6121,31 @@
         <v>20330051920367</v>
       </c>
       <c r="B23" t="s">
-        <v>431</v>
+        <v>275</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>632</v>
+        <v>482</v>
       </c>
       <c r="E23" t="s">
-        <v>664</v>
+        <v>514</v>
       </c>
       <c r="F23" t="s">
-        <v>696</v>
+        <v>546</v>
       </c>
       <c r="G23" t="s">
-        <v>696</v>
+        <v>546</v>
       </c>
       <c r="H23" t="s">
-        <v>743</v>
+        <v>593</v>
       </c>
       <c r="I23" t="s">
-        <v>770</v>
+        <v>620</v>
       </c>
       <c r="J23" t="s">
-        <v>696</v>
+        <v>546</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -7261,31 +6153,31 @@
         <v>20330051920100</v>
       </c>
       <c r="B24" t="s">
-        <v>596</v>
+        <v>443</v>
       </c>
       <c r="C24" t="s">
-        <v>609</v>
+        <v>459</v>
       </c>
       <c r="D24" t="s">
-        <v>633</v>
+        <v>483</v>
       </c>
       <c r="E24" t="s">
-        <v>665</v>
+        <v>515</v>
       </c>
       <c r="F24" t="s">
-        <v>697</v>
+        <v>547</v>
       </c>
       <c r="G24" t="s">
-        <v>716</v>
+        <v>566</v>
       </c>
       <c r="H24" t="s">
-        <v>744</v>
+        <v>594</v>
       </c>
       <c r="I24" t="s">
-        <v>771</v>
+        <v>621</v>
       </c>
       <c r="J24" t="s">
-        <v>697</v>
+        <v>547</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -7293,31 +6185,31 @@
         <v>20330051920101</v>
       </c>
       <c r="B25" t="s">
-        <v>272</v>
+        <v>444</v>
       </c>
       <c r="C25" t="s">
-        <v>610</v>
+        <v>460</v>
       </c>
       <c r="D25" t="s">
-        <v>634</v>
+        <v>484</v>
       </c>
       <c r="E25" t="s">
-        <v>666</v>
+        <v>516</v>
       </c>
       <c r="F25" t="s">
-        <v>698</v>
+        <v>548</v>
       </c>
       <c r="G25" t="s">
-        <v>698</v>
+        <v>548</v>
       </c>
       <c r="H25" t="s">
-        <v>745</v>
+        <v>595</v>
       </c>
       <c r="I25" t="s">
-        <v>666</v>
+        <v>516</v>
       </c>
       <c r="J25" t="s">
-        <v>797</v>
+        <v>647</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -7325,28 +6217,28 @@
         <v>20330051920102</v>
       </c>
       <c r="B26" t="s">
-        <v>597</v>
+        <v>445</v>
       </c>
       <c r="C26" t="s">
-        <v>611</v>
+        <v>461</v>
       </c>
       <c r="D26" t="s">
-        <v>635</v>
+        <v>485</v>
       </c>
       <c r="E26" t="s">
-        <v>667</v>
+        <v>517</v>
       </c>
       <c r="F26" t="s">
-        <v>699</v>
+        <v>549</v>
       </c>
       <c r="G26" t="s">
-        <v>717</v>
+        <v>567</v>
       </c>
       <c r="H26" t="s">
-        <v>746</v>
+        <v>596</v>
       </c>
       <c r="I26" t="s">
-        <v>772</v>
+        <v>622</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -7354,28 +6246,28 @@
         <v>20330051920104</v>
       </c>
       <c r="B27" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="C27" t="s">
         <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>636</v>
+        <v>486</v>
       </c>
       <c r="E27" t="s">
-        <v>668</v>
+        <v>518</v>
       </c>
       <c r="F27" t="s">
-        <v>700</v>
+        <v>550</v>
       </c>
       <c r="G27" t="s">
-        <v>718</v>
+        <v>568</v>
       </c>
       <c r="H27" t="s">
-        <v>747</v>
+        <v>597</v>
       </c>
       <c r="J27" t="s">
-        <v>798</v>
+        <v>648</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -7389,25 +6281,25 @@
         <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>637</v>
+        <v>487</v>
       </c>
       <c r="E28" t="s">
-        <v>669</v>
+        <v>519</v>
       </c>
       <c r="F28" t="s">
-        <v>701</v>
+        <v>551</v>
       </c>
       <c r="G28" t="s">
-        <v>719</v>
+        <v>569</v>
       </c>
       <c r="H28" t="s">
-        <v>748</v>
+        <v>598</v>
       </c>
       <c r="I28" t="s">
-        <v>773</v>
+        <v>623</v>
       </c>
       <c r="J28" t="s">
-        <v>719</v>
+        <v>569</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -7421,22 +6313,22 @@
         <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>638</v>
+        <v>488</v>
       </c>
       <c r="E29" t="s">
-        <v>670</v>
+        <v>520</v>
       </c>
       <c r="F29" t="s">
-        <v>702</v>
+        <v>552</v>
       </c>
       <c r="G29" t="s">
-        <v>720</v>
+        <v>570</v>
       </c>
       <c r="H29" t="s">
-        <v>749</v>
+        <v>599</v>
       </c>
       <c r="J29" t="s">
-        <v>799</v>
+        <v>649</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -7444,28 +6336,28 @@
         <v>20330051920109</v>
       </c>
       <c r="B30" t="s">
-        <v>274</v>
+        <v>446</v>
       </c>
       <c r="C30" t="s">
-        <v>604</v>
+        <v>454</v>
       </c>
       <c r="D30" t="s">
-        <v>639</v>
+        <v>489</v>
       </c>
       <c r="E30" t="s">
-        <v>671</v>
+        <v>521</v>
       </c>
       <c r="F30" t="s">
-        <v>703</v>
+        <v>553</v>
       </c>
       <c r="H30" t="s">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="I30" t="s">
-        <v>774</v>
+        <v>624</v>
       </c>
       <c r="J30" t="s">
-        <v>800</v>
+        <v>650</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -7473,28 +6365,28 @@
         <v>20330051920111</v>
       </c>
       <c r="B31" t="s">
-        <v>598</v>
+        <v>447</v>
       </c>
       <c r="C31" t="s">
-        <v>426</v>
+        <v>269</v>
       </c>
       <c r="D31" t="s">
-        <v>640</v>
+        <v>490</v>
       </c>
       <c r="E31" t="s">
-        <v>672</v>
+        <v>522</v>
       </c>
       <c r="F31" t="s">
-        <v>704</v>
+        <v>554</v>
       </c>
       <c r="H31" t="s">
-        <v>751</v>
+        <v>601</v>
       </c>
       <c r="I31" t="s">
-        <v>775</v>
+        <v>625</v>
       </c>
       <c r="J31" t="s">
-        <v>801</v>
+        <v>651</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -7502,31 +6394,31 @@
         <v>20330051920112</v>
       </c>
       <c r="B32" t="s">
-        <v>599</v>
+        <v>448</v>
       </c>
       <c r="C32" t="s">
         <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>641</v>
+        <v>491</v>
       </c>
       <c r="E32" t="s">
-        <v>673</v>
+        <v>523</v>
       </c>
       <c r="F32" t="s">
-        <v>705</v>
+        <v>555</v>
       </c>
       <c r="G32" t="s">
-        <v>721</v>
+        <v>571</v>
       </c>
       <c r="H32" t="s">
-        <v>752</v>
+        <v>602</v>
       </c>
       <c r="I32" t="s">
-        <v>776</v>
+        <v>626</v>
       </c>
       <c r="J32" t="s">
-        <v>802</v>
+        <v>652</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -7534,31 +6426,31 @@
         <v>20330051920113</v>
       </c>
       <c r="B33" t="s">
-        <v>286</v>
+        <v>449</v>
       </c>
       <c r="C33" t="s">
-        <v>433</v>
+        <v>277</v>
       </c>
       <c r="D33" t="s">
-        <v>642</v>
+        <v>492</v>
       </c>
       <c r="E33" t="s">
-        <v>674</v>
+        <v>524</v>
       </c>
       <c r="F33" t="s">
-        <v>706</v>
+        <v>556</v>
       </c>
       <c r="G33" t="s">
-        <v>706</v>
+        <v>556</v>
       </c>
       <c r="H33" t="s">
-        <v>753</v>
+        <v>603</v>
       </c>
       <c r="I33" t="s">
-        <v>777</v>
+        <v>627</v>
       </c>
       <c r="J33" t="s">
-        <v>803</v>
+        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -7566,7 +6458,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7617,28 +6509,28 @@
         <v>20330051920283</v>
       </c>
       <c r="B2" t="s">
-        <v>804</v>
+        <v>654</v>
       </c>
       <c r="C2" t="s">
         <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>834</v>
+        <v>689</v>
       </c>
       <c r="E2" t="s">
-        <v>867</v>
+        <v>723</v>
       </c>
       <c r="F2" t="s">
-        <v>902</v>
+        <v>758</v>
       </c>
       <c r="H2" t="s">
-        <v>953</v>
+        <v>811</v>
       </c>
       <c r="I2" t="s">
-        <v>987</v>
+        <v>846</v>
       </c>
       <c r="J2" t="s">
-        <v>1012</v>
+        <v>873</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -7646,31 +6538,31 @@
         <v>20330051920284</v>
       </c>
       <c r="B3" t="s">
-        <v>805</v>
+        <v>655</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>835</v>
+        <v>690</v>
       </c>
       <c r="E3" t="s">
-        <v>868</v>
+        <v>724</v>
       </c>
       <c r="F3" t="s">
-        <v>903</v>
+        <v>759</v>
       </c>
       <c r="G3" t="s">
-        <v>936</v>
+        <v>793</v>
       </c>
       <c r="H3" t="s">
-        <v>954</v>
+        <v>812</v>
       </c>
       <c r="I3" t="s">
-        <v>988</v>
+        <v>847</v>
       </c>
       <c r="J3" t="s">
-        <v>1013</v>
+        <v>874</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -7678,28 +6570,28 @@
         <v>20330051920285</v>
       </c>
       <c r="B4" t="s">
-        <v>806</v>
+        <v>656</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>836</v>
+        <v>691</v>
       </c>
       <c r="E4" t="s">
-        <v>869</v>
+        <v>725</v>
       </c>
       <c r="F4" t="s">
-        <v>904</v>
+        <v>760</v>
       </c>
       <c r="G4" t="s">
-        <v>937</v>
+        <v>794</v>
       </c>
       <c r="H4" t="s">
-        <v>955</v>
+        <v>813</v>
       </c>
       <c r="I4" t="s">
-        <v>989</v>
+        <v>848</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -7707,31 +6599,31 @@
         <v>20330051920286</v>
       </c>
       <c r="B5" t="s">
-        <v>807</v>
+        <v>657</v>
       </c>
       <c r="C5" t="s">
         <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>837</v>
+        <v>692</v>
       </c>
       <c r="E5" t="s">
-        <v>870</v>
+        <v>726</v>
       </c>
       <c r="F5" t="s">
-        <v>905</v>
+        <v>761</v>
       </c>
       <c r="G5" t="s">
-        <v>938</v>
+        <v>795</v>
       </c>
       <c r="H5" t="s">
-        <v>956</v>
+        <v>814</v>
       </c>
       <c r="I5" t="s">
-        <v>990</v>
+        <v>849</v>
       </c>
       <c r="J5" t="s">
-        <v>1014</v>
+        <v>875</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7739,31 +6631,31 @@
         <v>20330051920390</v>
       </c>
       <c r="B6" t="s">
-        <v>808</v>
+        <v>658</v>
       </c>
       <c r="C6" t="s">
-        <v>591</v>
+        <v>437</v>
       </c>
       <c r="D6" t="s">
-        <v>838</v>
+        <v>693</v>
       </c>
       <c r="E6" t="s">
-        <v>871</v>
+        <v>727</v>
       </c>
       <c r="F6" t="s">
-        <v>906</v>
+        <v>762</v>
       </c>
       <c r="G6" t="s">
-        <v>939</v>
+        <v>796</v>
       </c>
       <c r="H6" t="s">
-        <v>957</v>
+        <v>815</v>
       </c>
       <c r="I6" t="s">
-        <v>991</v>
+        <v>850</v>
       </c>
       <c r="J6" t="s">
-        <v>1015</v>
+        <v>876</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -7771,31 +6663,31 @@
         <v>20330051920287</v>
       </c>
       <c r="B7" t="s">
-        <v>809</v>
+        <v>659</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>839</v>
+        <v>694</v>
       </c>
       <c r="E7" t="s">
-        <v>872</v>
+        <v>728</v>
       </c>
       <c r="F7" t="s">
-        <v>907</v>
+        <v>763</v>
       </c>
       <c r="G7" t="s">
-        <v>907</v>
+        <v>763</v>
       </c>
       <c r="H7" t="s">
-        <v>958</v>
+        <v>816</v>
       </c>
       <c r="I7" t="s">
-        <v>992</v>
+        <v>851</v>
       </c>
       <c r="J7" t="s">
-        <v>1016</v>
+        <v>877</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -7803,31 +6695,31 @@
         <v>20330051920288</v>
       </c>
       <c r="B8" t="s">
-        <v>810</v>
+        <v>660</v>
       </c>
       <c r="C8" t="s">
-        <v>821</v>
+        <v>674</v>
       </c>
       <c r="D8" t="s">
-        <v>840</v>
+        <v>695</v>
       </c>
       <c r="E8" t="s">
-        <v>873</v>
+        <v>729</v>
       </c>
       <c r="F8" t="s">
-        <v>908</v>
+        <v>764</v>
       </c>
       <c r="G8" t="s">
-        <v>940</v>
+        <v>797</v>
       </c>
       <c r="H8" t="s">
-        <v>959</v>
+        <v>817</v>
       </c>
       <c r="I8" t="s">
-        <v>873</v>
+        <v>729</v>
       </c>
       <c r="J8" t="s">
-        <v>1017</v>
+        <v>878</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -7835,31 +6727,31 @@
         <v>20330051920290</v>
       </c>
       <c r="B9" t="s">
-        <v>591</v>
+        <v>437</v>
       </c>
       <c r="C9" t="s">
-        <v>822</v>
+        <v>675</v>
       </c>
       <c r="D9" t="s">
         <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>874</v>
+        <v>730</v>
       </c>
       <c r="F9" t="s">
-        <v>909</v>
+        <v>765</v>
       </c>
       <c r="G9" t="s">
-        <v>941</v>
+        <v>798</v>
       </c>
       <c r="H9" t="s">
-        <v>960</v>
+        <v>818</v>
       </c>
       <c r="I9" t="s">
-        <v>993</v>
+        <v>852</v>
       </c>
       <c r="J9" t="s">
-        <v>1018</v>
+        <v>879</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -7870,28 +6762,28 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>823</v>
+        <v>676</v>
       </c>
       <c r="D10" t="s">
-        <v>841</v>
+        <v>696</v>
       </c>
       <c r="E10" t="s">
-        <v>875</v>
+        <v>731</v>
       </c>
       <c r="F10" t="s">
-        <v>910</v>
+        <v>766</v>
       </c>
       <c r="G10" t="s">
-        <v>942</v>
+        <v>799</v>
       </c>
       <c r="H10" t="s">
-        <v>961</v>
+        <v>819</v>
       </c>
       <c r="I10" t="s">
-        <v>994</v>
+        <v>853</v>
       </c>
       <c r="J10" t="s">
-        <v>1019</v>
+        <v>880</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -7899,22 +6791,22 @@
         <v>20330051920293</v>
       </c>
       <c r="B11" t="s">
-        <v>811</v>
+        <v>661</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>842</v>
+        <v>697</v>
       </c>
       <c r="E11" t="s">
-        <v>876</v>
+        <v>732</v>
       </c>
       <c r="F11" t="s">
-        <v>911</v>
+        <v>767</v>
       </c>
       <c r="H11" t="s">
-        <v>962</v>
+        <v>820</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -7922,31 +6814,31 @@
         <v>20330051920294</v>
       </c>
       <c r="B12" t="s">
-        <v>812</v>
+        <v>662</v>
       </c>
       <c r="C12" t="s">
-        <v>824</v>
+        <v>677</v>
       </c>
       <c r="D12" t="s">
-        <v>843</v>
+        <v>698</v>
       </c>
       <c r="E12" t="s">
-        <v>877</v>
+        <v>733</v>
       </c>
       <c r="F12" t="s">
-        <v>912</v>
+        <v>768</v>
       </c>
       <c r="G12" t="s">
-        <v>943</v>
+        <v>800</v>
       </c>
       <c r="H12" t="s">
-        <v>963</v>
+        <v>821</v>
       </c>
       <c r="I12" t="s">
-        <v>995</v>
+        <v>854</v>
       </c>
       <c r="J12" t="s">
-        <v>1020</v>
+        <v>881</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -7957,28 +6849,28 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>273</v>
+        <v>669</v>
       </c>
       <c r="D13" t="s">
-        <v>844</v>
+        <v>699</v>
       </c>
       <c r="E13" t="s">
-        <v>878</v>
+        <v>734</v>
       </c>
       <c r="F13" t="s">
-        <v>913</v>
+        <v>769</v>
       </c>
       <c r="G13" t="s">
-        <v>913</v>
+        <v>769</v>
       </c>
       <c r="H13" t="s">
-        <v>964</v>
+        <v>822</v>
       </c>
       <c r="I13" t="s">
-        <v>996</v>
+        <v>855</v>
       </c>
       <c r="J13" t="s">
-        <v>1021</v>
+        <v>882</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -7989,28 +6881,28 @@
         <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>825</v>
+        <v>678</v>
       </c>
       <c r="D14" t="s">
-        <v>845</v>
+        <v>700</v>
       </c>
       <c r="E14" t="s">
-        <v>879</v>
+        <v>735</v>
       </c>
       <c r="F14" t="s">
-        <v>914</v>
+        <v>770</v>
       </c>
       <c r="G14" t="s">
-        <v>944</v>
+        <v>801</v>
       </c>
       <c r="H14" t="s">
-        <v>965</v>
+        <v>823</v>
       </c>
       <c r="I14" t="s">
-        <v>879</v>
+        <v>735</v>
       </c>
       <c r="J14" t="s">
-        <v>944</v>
+        <v>801</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -8021,28 +6913,28 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>826</v>
+        <v>679</v>
       </c>
       <c r="D15" t="s">
-        <v>846</v>
+        <v>701</v>
       </c>
       <c r="E15" t="s">
-        <v>880</v>
+        <v>736</v>
       </c>
       <c r="F15" t="s">
-        <v>915</v>
+        <v>771</v>
       </c>
       <c r="G15" t="s">
-        <v>945</v>
+        <v>802</v>
       </c>
       <c r="H15" t="s">
-        <v>966</v>
+        <v>824</v>
       </c>
       <c r="I15" t="s">
-        <v>997</v>
+        <v>856</v>
       </c>
       <c r="J15" t="s">
-        <v>945</v>
+        <v>802</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -8053,25 +6945,25 @@
         <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D16" t="s">
-        <v>847</v>
+        <v>702</v>
       </c>
       <c r="E16" t="s">
-        <v>881</v>
+        <v>737</v>
       </c>
       <c r="F16" t="s">
-        <v>916</v>
+        <v>772</v>
       </c>
       <c r="H16" t="s">
-        <v>967</v>
+        <v>825</v>
       </c>
       <c r="I16" t="s">
-        <v>998</v>
+        <v>857</v>
       </c>
       <c r="J16" t="s">
-        <v>1022</v>
+        <v>883</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -8079,25 +6971,25 @@
         <v>20330051920298</v>
       </c>
       <c r="B17" t="s">
-        <v>813</v>
+        <v>663</v>
       </c>
       <c r="C17" t="s">
-        <v>606</v>
+        <v>456</v>
       </c>
       <c r="D17" t="s">
-        <v>848</v>
+        <v>703</v>
       </c>
       <c r="E17" t="s">
-        <v>882</v>
+        <v>738</v>
       </c>
       <c r="F17" t="s">
-        <v>917</v>
+        <v>773</v>
       </c>
       <c r="H17" t="s">
-        <v>968</v>
+        <v>826</v>
       </c>
       <c r="J17" t="s">
-        <v>1023</v>
+        <v>884</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -8108,25 +7000,25 @@
         <v>21</v>
       </c>
       <c r="C18" t="s">
+        <v>680</v>
+      </c>
+      <c r="D18" t="s">
+        <v>704</v>
+      </c>
+      <c r="E18" t="s">
+        <v>739</v>
+      </c>
+      <c r="F18" t="s">
+        <v>774</v>
+      </c>
+      <c r="H18" t="s">
         <v>827</v>
       </c>
-      <c r="D18" t="s">
-        <v>849</v>
-      </c>
-      <c r="E18" t="s">
-        <v>883</v>
-      </c>
-      <c r="F18" t="s">
-        <v>918</v>
-      </c>
-      <c r="H18" t="s">
-        <v>969</v>
-      </c>
       <c r="I18" t="s">
-        <v>999</v>
+        <v>858</v>
       </c>
       <c r="J18" t="s">
-        <v>1024</v>
+        <v>885</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -8134,31 +7026,31 @@
         <v>20330051920300</v>
       </c>
       <c r="B19" t="s">
-        <v>269</v>
+        <v>664</v>
       </c>
       <c r="C19" t="s">
-        <v>285</v>
+        <v>681</v>
       </c>
       <c r="D19" t="s">
-        <v>850</v>
+        <v>705</v>
       </c>
       <c r="E19" t="s">
-        <v>884</v>
+        <v>740</v>
       </c>
       <c r="F19" t="s">
-        <v>919</v>
+        <v>775</v>
       </c>
       <c r="G19" t="s">
-        <v>357</v>
+        <v>803</v>
       </c>
       <c r="H19" t="s">
-        <v>374</v>
+        <v>828</v>
       </c>
       <c r="I19" t="s">
-        <v>395</v>
+        <v>859</v>
       </c>
       <c r="J19" t="s">
-        <v>1025</v>
+        <v>886</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -8172,25 +7064,25 @@
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>851</v>
+        <v>706</v>
       </c>
       <c r="E20" t="s">
-        <v>885</v>
+        <v>741</v>
       </c>
       <c r="F20" t="s">
-        <v>920</v>
+        <v>776</v>
       </c>
       <c r="G20" t="s">
-        <v>920</v>
+        <v>776</v>
       </c>
       <c r="H20" t="s">
-        <v>970</v>
+        <v>829</v>
       </c>
       <c r="I20" t="s">
-        <v>1000</v>
+        <v>860</v>
       </c>
       <c r="J20" t="s">
-        <v>1026</v>
+        <v>887</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -8204,25 +7096,25 @@
         <v>32</v>
       </c>
       <c r="D21" t="s">
-        <v>852</v>
+        <v>707</v>
       </c>
       <c r="E21" t="s">
-        <v>886</v>
+        <v>742</v>
       </c>
       <c r="F21" t="s">
-        <v>343</v>
+        <v>777</v>
       </c>
       <c r="G21" t="s">
-        <v>343</v>
+        <v>777</v>
       </c>
       <c r="H21" t="s">
-        <v>971</v>
+        <v>830</v>
       </c>
       <c r="I21" t="s">
-        <v>397</v>
+        <v>861</v>
       </c>
       <c r="J21" t="s">
-        <v>1027</v>
+        <v>888</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -8230,31 +7122,31 @@
         <v>20330051920303</v>
       </c>
       <c r="B22" t="s">
-        <v>814</v>
+        <v>665</v>
       </c>
       <c r="C22" t="s">
-        <v>828</v>
+        <v>682</v>
       </c>
       <c r="D22" t="s">
-        <v>853</v>
+        <v>708</v>
       </c>
       <c r="E22" t="s">
-        <v>887</v>
+        <v>743</v>
       </c>
       <c r="F22" t="s">
-        <v>921</v>
+        <v>778</v>
       </c>
       <c r="G22" t="s">
-        <v>946</v>
+        <v>804</v>
       </c>
       <c r="H22" t="s">
-        <v>972</v>
+        <v>831</v>
       </c>
       <c r="I22" t="s">
-        <v>1001</v>
+        <v>862</v>
       </c>
       <c r="J22" t="s">
-        <v>1028</v>
+        <v>889</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -8262,31 +7154,31 @@
         <v>19330061460416</v>
       </c>
       <c r="B23" t="s">
-        <v>815</v>
+        <v>666</v>
       </c>
       <c r="C23" t="s">
-        <v>829</v>
+        <v>683</v>
       </c>
       <c r="D23" t="s">
-        <v>854</v>
+        <v>709</v>
       </c>
       <c r="E23" t="s">
-        <v>888</v>
+        <v>744</v>
       </c>
       <c r="F23" t="s">
-        <v>922</v>
+        <v>779</v>
       </c>
       <c r="G23" t="s">
-        <v>947</v>
+        <v>805</v>
       </c>
       <c r="H23" t="s">
-        <v>973</v>
+        <v>832</v>
       </c>
       <c r="I23" t="s">
-        <v>1002</v>
+        <v>863</v>
       </c>
       <c r="J23" t="s">
-        <v>1029</v>
+        <v>890</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -8294,31 +7186,31 @@
         <v>19330051920208</v>
       </c>
       <c r="B24" t="s">
-        <v>816</v>
+        <v>667</v>
       </c>
       <c r="C24" t="s">
-        <v>422</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>855</v>
+        <v>710</v>
       </c>
       <c r="E24" t="s">
-        <v>889</v>
+        <v>745</v>
       </c>
       <c r="F24" t="s">
-        <v>923</v>
+        <v>780</v>
       </c>
       <c r="G24" t="s">
-        <v>923</v>
+        <v>780</v>
       </c>
       <c r="H24" t="s">
-        <v>974</v>
+        <v>833</v>
       </c>
       <c r="I24" t="s">
-        <v>1003</v>
+        <v>864</v>
       </c>
       <c r="J24" t="s">
-        <v>1030</v>
+        <v>891</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -8326,31 +7218,31 @@
         <v>20330051920304</v>
       </c>
       <c r="B25" t="s">
-        <v>817</v>
+        <v>668</v>
       </c>
       <c r="C25" t="s">
-        <v>830</v>
+        <v>684</v>
       </c>
       <c r="D25" t="s">
-        <v>856</v>
+        <v>711</v>
       </c>
       <c r="E25" t="s">
-        <v>890</v>
+        <v>746</v>
       </c>
       <c r="F25" t="s">
-        <v>924</v>
+        <v>781</v>
       </c>
       <c r="G25" t="s">
-        <v>924</v>
+        <v>781</v>
       </c>
       <c r="H25" t="s">
-        <v>975</v>
+        <v>834</v>
       </c>
       <c r="I25" t="s">
-        <v>890</v>
+        <v>746</v>
       </c>
       <c r="J25" t="s">
-        <v>1031</v>
+        <v>892</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -8364,25 +7256,25 @@
         <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>857</v>
+        <v>712</v>
       </c>
       <c r="E26" t="s">
-        <v>891</v>
+        <v>747</v>
       </c>
       <c r="F26" t="s">
-        <v>925</v>
+        <v>782</v>
       </c>
       <c r="G26" t="s">
-        <v>925</v>
+        <v>782</v>
       </c>
       <c r="H26" t="s">
-        <v>976</v>
+        <v>835</v>
       </c>
       <c r="I26" t="s">
-        <v>1004</v>
+        <v>865</v>
       </c>
       <c r="J26" t="s">
-        <v>1032</v>
+        <v>893</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -8390,25 +7282,25 @@
         <v>20330051920308</v>
       </c>
       <c r="B27" t="s">
-        <v>273</v>
+        <v>669</v>
       </c>
       <c r="C27" t="s">
         <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>306</v>
+        <v>713</v>
       </c>
       <c r="E27" t="s">
-        <v>892</v>
+        <v>748</v>
       </c>
       <c r="F27" t="s">
-        <v>926</v>
+        <v>783</v>
       </c>
       <c r="H27" t="s">
-        <v>977</v>
+        <v>836</v>
       </c>
       <c r="J27" t="s">
-        <v>1033</v>
+        <v>894</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -8416,31 +7308,31 @@
         <v>20330051920309</v>
       </c>
       <c r="B28" t="s">
-        <v>273</v>
+        <v>669</v>
       </c>
       <c r="C28" t="s">
-        <v>831</v>
+        <v>685</v>
       </c>
       <c r="D28" t="s">
-        <v>858</v>
+        <v>714</v>
       </c>
       <c r="E28" t="s">
-        <v>893</v>
+        <v>749</v>
       </c>
       <c r="F28" t="s">
-        <v>927</v>
+        <v>784</v>
       </c>
       <c r="G28" t="s">
-        <v>948</v>
+        <v>806</v>
       </c>
       <c r="H28" t="s">
-        <v>978</v>
+        <v>837</v>
       </c>
       <c r="I28" t="s">
-        <v>1005</v>
+        <v>866</v>
       </c>
       <c r="J28" t="s">
-        <v>1034</v>
+        <v>895</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -8448,31 +7340,31 @@
         <v>20330051920310</v>
       </c>
       <c r="B29" t="s">
-        <v>287</v>
+        <v>670</v>
       </c>
       <c r="C29" t="s">
         <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>859</v>
+        <v>715</v>
       </c>
       <c r="E29" t="s">
-        <v>894</v>
+        <v>750</v>
       </c>
       <c r="F29" t="s">
-        <v>928</v>
+        <v>785</v>
       </c>
       <c r="G29" t="s">
-        <v>949</v>
+        <v>807</v>
       </c>
       <c r="H29" t="s">
-        <v>979</v>
+        <v>838</v>
       </c>
       <c r="I29" t="s">
-        <v>1006</v>
+        <v>867</v>
       </c>
       <c r="J29" t="s">
-        <v>1035</v>
+        <v>896</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -8480,28 +7372,28 @@
         <v>20330051920311</v>
       </c>
       <c r="B30" t="s">
-        <v>818</v>
+        <v>671</v>
       </c>
       <c r="C30" t="s">
-        <v>818</v>
+        <v>671</v>
       </c>
       <c r="D30" t="s">
-        <v>860</v>
+        <v>716</v>
       </c>
       <c r="E30" t="s">
-        <v>895</v>
+        <v>751</v>
       </c>
       <c r="F30" t="s">
-        <v>929</v>
+        <v>786</v>
       </c>
       <c r="H30" t="s">
-        <v>980</v>
+        <v>839</v>
       </c>
       <c r="I30" t="s">
-        <v>895</v>
+        <v>751</v>
       </c>
       <c r="J30" t="s">
-        <v>1036</v>
+        <v>897</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -8512,28 +7404,28 @@
         <v>45</v>
       </c>
       <c r="C31" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D31" t="s">
-        <v>861</v>
+        <v>717</v>
       </c>
       <c r="E31" t="s">
-        <v>896</v>
+        <v>752</v>
       </c>
       <c r="F31" t="s">
-        <v>930</v>
+        <v>787</v>
       </c>
       <c r="G31" t="s">
-        <v>930</v>
+        <v>787</v>
       </c>
       <c r="H31" t="s">
-        <v>981</v>
+        <v>840</v>
       </c>
       <c r="I31" t="s">
-        <v>1007</v>
+        <v>868</v>
       </c>
       <c r="J31" t="s">
-        <v>1037</v>
+        <v>898</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -8547,19 +7439,19 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>862</v>
+        <v>718</v>
       </c>
       <c r="E32" t="s">
-        <v>897</v>
+        <v>753</v>
       </c>
       <c r="F32" t="s">
-        <v>931</v>
+        <v>788</v>
       </c>
       <c r="H32" t="s">
-        <v>982</v>
+        <v>841</v>
       </c>
       <c r="J32" t="s">
-        <v>1038</v>
+        <v>899</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -8570,28 +7462,28 @@
         <v>38</v>
       </c>
       <c r="C33" t="s">
-        <v>284</v>
+        <v>686</v>
       </c>
       <c r="D33" t="s">
-        <v>863</v>
+        <v>719</v>
       </c>
       <c r="E33" t="s">
-        <v>898</v>
+        <v>754</v>
       </c>
       <c r="F33" t="s">
-        <v>932</v>
+        <v>789</v>
       </c>
       <c r="G33" t="s">
-        <v>950</v>
+        <v>808</v>
       </c>
       <c r="H33" t="s">
-        <v>983</v>
+        <v>842</v>
       </c>
       <c r="I33" t="s">
-        <v>1008</v>
+        <v>869</v>
       </c>
       <c r="J33" t="s">
-        <v>1039</v>
+        <v>900</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -8602,28 +7494,28 @@
         <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>434</v>
+        <v>278</v>
       </c>
       <c r="D34" t="s">
-        <v>864</v>
+        <v>720</v>
       </c>
       <c r="E34" t="s">
-        <v>899</v>
+        <v>755</v>
       </c>
       <c r="F34" t="s">
-        <v>933</v>
+        <v>790</v>
       </c>
       <c r="G34" t="s">
-        <v>933</v>
+        <v>790</v>
       </c>
       <c r="H34" t="s">
-        <v>984</v>
+        <v>843</v>
       </c>
       <c r="I34" t="s">
-        <v>1009</v>
+        <v>870</v>
       </c>
       <c r="J34" t="s">
-        <v>1040</v>
+        <v>901</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -8631,31 +7523,31 @@
         <v>20330051920314</v>
       </c>
       <c r="B35" t="s">
-        <v>819</v>
+        <v>672</v>
       </c>
       <c r="C35" t="s">
-        <v>832</v>
+        <v>687</v>
       </c>
       <c r="D35" t="s">
-        <v>865</v>
+        <v>721</v>
       </c>
       <c r="E35" t="s">
-        <v>900</v>
+        <v>756</v>
       </c>
       <c r="F35" t="s">
-        <v>934</v>
+        <v>791</v>
       </c>
       <c r="G35" t="s">
-        <v>951</v>
+        <v>809</v>
       </c>
       <c r="H35" t="s">
-        <v>985</v>
+        <v>844</v>
       </c>
       <c r="I35" t="s">
-        <v>1010</v>
+        <v>871</v>
       </c>
       <c r="J35" t="s">
-        <v>1041</v>
+        <v>902</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -8663,31 +7555,31 @@
         <v>20330051920316</v>
       </c>
       <c r="B36" t="s">
-        <v>820</v>
+        <v>673</v>
       </c>
       <c r="C36" t="s">
-        <v>833</v>
+        <v>688</v>
       </c>
       <c r="D36" t="s">
-        <v>866</v>
+        <v>722</v>
       </c>
       <c r="E36" t="s">
-        <v>901</v>
+        <v>757</v>
       </c>
       <c r="F36" t="s">
-        <v>935</v>
+        <v>792</v>
       </c>
       <c r="G36" t="s">
-        <v>952</v>
+        <v>810</v>
       </c>
       <c r="H36" t="s">
-        <v>986</v>
+        <v>845</v>
       </c>
       <c r="I36" t="s">
-        <v>1011</v>
+        <v>872</v>
       </c>
       <c r="J36" t="s">
-        <v>1042</v>
+        <v>903</v>
       </c>
     </row>
   </sheetData>
@@ -8695,7 +7587,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8746,28 +7638,28 @@
         <v>20330051920336</v>
       </c>
       <c r="B2" t="s">
-        <v>1043</v>
+        <v>904</v>
       </c>
       <c r="C2" t="s">
-        <v>1052</v>
+        <v>914</v>
       </c>
       <c r="D2" t="s">
-        <v>1063</v>
+        <v>926</v>
       </c>
       <c r="E2" t="s">
-        <v>1080</v>
+        <v>943</v>
       </c>
       <c r="F2" t="s">
-        <v>1105</v>
+        <v>968</v>
       </c>
       <c r="H2" t="s">
-        <v>1141</v>
+        <v>1004</v>
       </c>
       <c r="I2" t="s">
-        <v>1166</v>
+        <v>1029</v>
       </c>
       <c r="J2" t="s">
-        <v>1187</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -8778,25 +7670,25 @@
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>1053</v>
+        <v>915</v>
       </c>
       <c r="D3" t="s">
-        <v>1064</v>
+        <v>927</v>
       </c>
       <c r="E3" t="s">
-        <v>1081</v>
+        <v>944</v>
       </c>
       <c r="F3" t="s">
-        <v>1106</v>
+        <v>969</v>
       </c>
       <c r="H3" t="s">
-        <v>1142</v>
+        <v>1005</v>
       </c>
       <c r="I3" t="s">
-        <v>1167</v>
+        <v>1030</v>
       </c>
       <c r="J3" t="s">
-        <v>1188</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -8807,28 +7699,28 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>1054</v>
+        <v>916</v>
       </c>
       <c r="D4" t="s">
-        <v>1065</v>
+        <v>928</v>
       </c>
       <c r="E4" t="s">
-        <v>1082</v>
+        <v>945</v>
       </c>
       <c r="F4" t="s">
-        <v>1107</v>
+        <v>970</v>
       </c>
       <c r="G4" t="s">
-        <v>1130</v>
+        <v>993</v>
       </c>
       <c r="H4" t="s">
-        <v>1143</v>
+        <v>1006</v>
       </c>
       <c r="I4" t="s">
-        <v>1168</v>
+        <v>1031</v>
       </c>
       <c r="J4" t="s">
-        <v>1189</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -8836,31 +7728,31 @@
         <v>20330051920339</v>
       </c>
       <c r="B5" t="s">
-        <v>1044</v>
+        <v>905</v>
       </c>
       <c r="C5" t="s">
-        <v>277</v>
+        <v>917</v>
       </c>
       <c r="D5" t="s">
-        <v>1046</v>
+        <v>907</v>
       </c>
       <c r="E5" t="s">
-        <v>1083</v>
+        <v>946</v>
       </c>
       <c r="F5" t="s">
-        <v>1108</v>
+        <v>971</v>
       </c>
       <c r="G5" t="s">
-        <v>1131</v>
+        <v>994</v>
       </c>
       <c r="H5" t="s">
-        <v>1144</v>
+        <v>1007</v>
       </c>
       <c r="I5" t="s">
-        <v>1169</v>
+        <v>1032</v>
       </c>
       <c r="J5" t="s">
-        <v>1190</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -8868,31 +7760,31 @@
         <v>20330051920340</v>
       </c>
       <c r="B6" t="s">
-        <v>1045</v>
+        <v>906</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>622</v>
+        <v>472</v>
       </c>
       <c r="E6" t="s">
-        <v>1084</v>
+        <v>947</v>
       </c>
       <c r="F6" t="s">
-        <v>1109</v>
+        <v>972</v>
       </c>
       <c r="G6" t="s">
-        <v>1109</v>
+        <v>972</v>
       </c>
       <c r="H6" t="s">
-        <v>1145</v>
+        <v>1008</v>
       </c>
       <c r="I6" t="s">
-        <v>1084</v>
+        <v>947</v>
       </c>
       <c r="J6" t="s">
-        <v>1109</v>
+        <v>972</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -8900,31 +7792,31 @@
         <v>20330051920341</v>
       </c>
       <c r="B7" t="s">
-        <v>591</v>
+        <v>437</v>
       </c>
       <c r="C7" t="s">
-        <v>1055</v>
+        <v>918</v>
       </c>
       <c r="D7" t="s">
-        <v>1066</v>
+        <v>929</v>
       </c>
       <c r="E7" t="s">
-        <v>1085</v>
+        <v>948</v>
       </c>
       <c r="F7" t="s">
-        <v>1110</v>
+        <v>973</v>
       </c>
       <c r="G7" t="s">
-        <v>1132</v>
+        <v>995</v>
       </c>
       <c r="H7" t="s">
-        <v>1146</v>
+        <v>1009</v>
       </c>
       <c r="I7" t="s">
-        <v>1170</v>
+        <v>1033</v>
       </c>
       <c r="J7" t="s">
-        <v>1132</v>
+        <v>995</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -8932,28 +7824,28 @@
         <v>20330051920342</v>
       </c>
       <c r="B8" t="s">
-        <v>591</v>
+        <v>437</v>
       </c>
       <c r="C8" t="s">
-        <v>1056</v>
+        <v>919</v>
       </c>
       <c r="D8" t="s">
-        <v>1067</v>
+        <v>930</v>
       </c>
       <c r="E8" t="s">
-        <v>1086</v>
+        <v>949</v>
       </c>
       <c r="F8" t="s">
-        <v>1111</v>
+        <v>974</v>
       </c>
       <c r="H8" t="s">
-        <v>1147</v>
+        <v>1010</v>
       </c>
       <c r="I8" t="s">
-        <v>1171</v>
+        <v>1034</v>
       </c>
       <c r="J8" t="s">
-        <v>1191</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -8961,31 +7853,31 @@
         <v>20330051920343</v>
       </c>
       <c r="B9" t="s">
-        <v>1046</v>
+        <v>907</v>
       </c>
       <c r="C9" t="s">
         <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>844</v>
+        <v>699</v>
       </c>
       <c r="E9" t="s">
-        <v>1087</v>
+        <v>950</v>
       </c>
       <c r="F9" t="s">
-        <v>1112</v>
+        <v>975</v>
       </c>
       <c r="G9" t="s">
-        <v>1133</v>
+        <v>996</v>
       </c>
       <c r="H9" t="s">
-        <v>1148</v>
+        <v>1011</v>
       </c>
       <c r="I9" t="s">
-        <v>1172</v>
+        <v>1035</v>
       </c>
       <c r="J9" t="s">
-        <v>1192</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -8996,25 +7888,25 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>1057</v>
+        <v>920</v>
       </c>
       <c r="D10" t="s">
-        <v>1068</v>
+        <v>931</v>
       </c>
       <c r="E10" t="s">
-        <v>1088</v>
+        <v>951</v>
       </c>
       <c r="F10" t="s">
-        <v>1113</v>
+        <v>976</v>
       </c>
       <c r="H10" t="s">
-        <v>1149</v>
+        <v>1012</v>
       </c>
       <c r="I10" t="s">
-        <v>1173</v>
+        <v>1036</v>
       </c>
       <c r="J10" t="s">
-        <v>1193</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -9025,25 +7917,25 @@
         <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>591</v>
+        <v>437</v>
       </c>
       <c r="D11" t="s">
-        <v>618</v>
+        <v>468</v>
       </c>
       <c r="E11" t="s">
-        <v>1089</v>
+        <v>952</v>
       </c>
       <c r="F11" t="s">
-        <v>1114</v>
+        <v>977</v>
       </c>
       <c r="H11" t="s">
-        <v>1150</v>
+        <v>1013</v>
       </c>
       <c r="I11" t="s">
-        <v>1174</v>
+        <v>1037</v>
       </c>
       <c r="J11" t="s">
-        <v>1194</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -9054,28 +7946,28 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
+        <v>921</v>
+      </c>
+      <c r="D12" t="s">
+        <v>932</v>
+      </c>
+      <c r="E12" t="s">
+        <v>953</v>
+      </c>
+      <c r="F12" t="s">
+        <v>978</v>
+      </c>
+      <c r="G12" t="s">
+        <v>978</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1014</v>
+      </c>
+      <c r="I12" t="s">
+        <v>1038</v>
+      </c>
+      <c r="J12" t="s">
         <v>1058</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1069</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1090</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G12" t="s">
-        <v>1115</v>
-      </c>
-      <c r="H12" t="s">
-        <v>1151</v>
-      </c>
-      <c r="I12" t="s">
-        <v>1175</v>
-      </c>
-      <c r="J12" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -9089,19 +7981,19 @@
         <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>1070</v>
+        <v>933</v>
       </c>
       <c r="E13" t="s">
-        <v>1091</v>
+        <v>954</v>
       </c>
       <c r="F13" t="s">
-        <v>1116</v>
+        <v>979</v>
       </c>
       <c r="G13" t="s">
-        <v>1134</v>
+        <v>997</v>
       </c>
       <c r="H13" t="s">
-        <v>1152</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -9112,28 +8004,28 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>1059</v>
+        <v>922</v>
       </c>
       <c r="D14" t="s">
-        <v>618</v>
+        <v>468</v>
       </c>
       <c r="E14" t="s">
-        <v>1092</v>
+        <v>955</v>
       </c>
       <c r="F14" t="s">
-        <v>1117</v>
+        <v>980</v>
       </c>
       <c r="G14" t="s">
-        <v>1117</v>
+        <v>980</v>
       </c>
       <c r="H14" t="s">
-        <v>1153</v>
+        <v>1016</v>
       </c>
       <c r="I14" t="s">
-        <v>1092</v>
+        <v>955</v>
       </c>
       <c r="J14" t="s">
-        <v>1117</v>
+        <v>980</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -9144,25 +8036,25 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>594</v>
+        <v>441</v>
       </c>
       <c r="D15" t="s">
-        <v>1071</v>
+        <v>934</v>
       </c>
       <c r="E15" t="s">
-        <v>1093</v>
+        <v>956</v>
       </c>
       <c r="F15" t="s">
-        <v>1118</v>
+        <v>981</v>
       </c>
       <c r="H15" t="s">
-        <v>1154</v>
+        <v>1017</v>
       </c>
       <c r="I15" t="s">
-        <v>1176</v>
+        <v>1039</v>
       </c>
       <c r="J15" t="s">
-        <v>1196</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -9170,31 +8062,31 @@
         <v>20330051920348</v>
       </c>
       <c r="B16" t="s">
-        <v>300</v>
+        <v>908</v>
       </c>
       <c r="C16" t="s">
+        <v>923</v>
+      </c>
+      <c r="D16" t="s">
+        <v>468</v>
+      </c>
+      <c r="E16" t="s">
+        <v>957</v>
+      </c>
+      <c r="F16" t="s">
+        <v>982</v>
+      </c>
+      <c r="G16" t="s">
+        <v>998</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I16" t="s">
+        <v>1040</v>
+      </c>
+      <c r="J16" t="s">
         <v>1060</v>
-      </c>
-      <c r="D16" t="s">
-        <v>618</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1094</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1119</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1135</v>
-      </c>
-      <c r="H16" t="s">
-        <v>1155</v>
-      </c>
-      <c r="I16" t="s">
-        <v>1177</v>
-      </c>
-      <c r="J16" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -9202,28 +8094,28 @@
         <v>20330051920349</v>
       </c>
       <c r="B17" t="s">
-        <v>1047</v>
+        <v>909</v>
       </c>
       <c r="C17" t="s">
+        <v>924</v>
+      </c>
+      <c r="D17" t="s">
+        <v>935</v>
+      </c>
+      <c r="E17" t="s">
+        <v>958</v>
+      </c>
+      <c r="F17" t="s">
+        <v>983</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1019</v>
+      </c>
+      <c r="I17" t="s">
+        <v>958</v>
+      </c>
+      <c r="J17" t="s">
         <v>1061</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1095</v>
-      </c>
-      <c r="F17" t="s">
-        <v>1120</v>
-      </c>
-      <c r="H17" t="s">
-        <v>1156</v>
-      </c>
-      <c r="I17" t="s">
-        <v>1095</v>
-      </c>
-      <c r="J17" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -9231,31 +8123,31 @@
         <v>20330051920350</v>
       </c>
       <c r="B18" t="s">
-        <v>1048</v>
+        <v>910</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>1073</v>
+        <v>936</v>
       </c>
       <c r="E18" t="s">
-        <v>1096</v>
+        <v>959</v>
       </c>
       <c r="F18" t="s">
-        <v>1121</v>
+        <v>984</v>
       </c>
       <c r="G18" t="s">
-        <v>1121</v>
+        <v>984</v>
       </c>
       <c r="H18" t="s">
-        <v>1157</v>
+        <v>1020</v>
       </c>
       <c r="I18" t="s">
-        <v>1178</v>
+        <v>1041</v>
       </c>
       <c r="J18" t="s">
-        <v>1199</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -9269,25 +8161,25 @@
         <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>1074</v>
+        <v>937</v>
       </c>
       <c r="E19" t="s">
-        <v>1097</v>
+        <v>960</v>
       </c>
       <c r="F19" t="s">
-        <v>1122</v>
+        <v>985</v>
       </c>
       <c r="G19" t="s">
-        <v>1136</v>
+        <v>999</v>
       </c>
       <c r="H19" t="s">
-        <v>1158</v>
+        <v>1021</v>
       </c>
       <c r="I19" t="s">
-        <v>1179</v>
+        <v>1042</v>
       </c>
       <c r="J19" t="s">
-        <v>1200</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -9301,25 +8193,25 @@
         <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>1075</v>
+        <v>938</v>
       </c>
       <c r="E20" t="s">
-        <v>1098</v>
+        <v>961</v>
       </c>
       <c r="F20" t="s">
-        <v>1123</v>
+        <v>986</v>
       </c>
       <c r="G20" t="s">
-        <v>1137</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="s">
-        <v>1159</v>
+        <v>1022</v>
       </c>
       <c r="I20" t="s">
-        <v>1180</v>
+        <v>1043</v>
       </c>
       <c r="J20" t="s">
-        <v>1137</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -9333,25 +8225,25 @@
         <v>52</v>
       </c>
       <c r="D21" t="s">
-        <v>1076</v>
+        <v>939</v>
       </c>
       <c r="E21" t="s">
-        <v>1099</v>
+        <v>962</v>
       </c>
       <c r="F21" t="s">
-        <v>1124</v>
+        <v>987</v>
       </c>
       <c r="G21" t="s">
-        <v>1124</v>
+        <v>987</v>
       </c>
       <c r="H21" t="s">
-        <v>1160</v>
+        <v>1023</v>
       </c>
       <c r="I21" t="s">
-        <v>1181</v>
+        <v>1044</v>
       </c>
       <c r="J21" t="s">
-        <v>1201</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -9359,31 +8251,31 @@
         <v>20330051920355</v>
       </c>
       <c r="B22" t="s">
-        <v>1049</v>
+        <v>911</v>
       </c>
       <c r="C22" t="s">
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>1071</v>
+        <v>934</v>
       </c>
       <c r="E22" t="s">
-        <v>1100</v>
+        <v>963</v>
       </c>
       <c r="F22" t="s">
-        <v>1125</v>
+        <v>988</v>
       </c>
       <c r="G22" t="s">
-        <v>1138</v>
+        <v>1001</v>
       </c>
       <c r="H22" t="s">
-        <v>1161</v>
+        <v>1024</v>
       </c>
       <c r="I22" t="s">
-        <v>1182</v>
+        <v>1045</v>
       </c>
       <c r="J22" t="s">
-        <v>1202</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -9391,31 +8283,31 @@
         <v>20330051920382</v>
       </c>
       <c r="B23" t="s">
-        <v>599</v>
+        <v>448</v>
       </c>
       <c r="C23" t="s">
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>1067</v>
+        <v>930</v>
       </c>
       <c r="E23" t="s">
-        <v>1101</v>
+        <v>964</v>
       </c>
       <c r="F23" t="s">
-        <v>1126</v>
+        <v>989</v>
       </c>
       <c r="G23" t="s">
-        <v>1126</v>
+        <v>989</v>
       </c>
       <c r="H23" t="s">
-        <v>1162</v>
+        <v>1025</v>
       </c>
       <c r="I23" t="s">
-        <v>1183</v>
+        <v>1046</v>
       </c>
       <c r="J23" t="s">
-        <v>1203</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -9423,28 +8315,28 @@
         <v>20330051920356</v>
       </c>
       <c r="B24" t="s">
-        <v>1050</v>
+        <v>912</v>
       </c>
       <c r="C24" t="s">
-        <v>1062</v>
+        <v>925</v>
       </c>
       <c r="D24" t="s">
-        <v>1077</v>
+        <v>940</v>
       </c>
       <c r="E24" t="s">
-        <v>1102</v>
+        <v>965</v>
       </c>
       <c r="F24" t="s">
-        <v>1127</v>
+        <v>990</v>
       </c>
       <c r="H24" t="s">
-        <v>1163</v>
+        <v>1026</v>
       </c>
       <c r="I24" t="s">
-        <v>1184</v>
+        <v>1047</v>
       </c>
       <c r="J24" t="s">
-        <v>1204</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -9452,31 +8344,31 @@
         <v>20330051920357</v>
       </c>
       <c r="B25" t="s">
-        <v>1051</v>
+        <v>913</v>
       </c>
       <c r="C25" t="s">
-        <v>439</v>
+        <v>283</v>
       </c>
       <c r="D25" t="s">
-        <v>1078</v>
+        <v>941</v>
       </c>
       <c r="E25" t="s">
-        <v>1103</v>
+        <v>966</v>
       </c>
       <c r="F25" t="s">
-        <v>1128</v>
+        <v>991</v>
       </c>
       <c r="G25" t="s">
-        <v>1139</v>
+        <v>1002</v>
       </c>
       <c r="H25" t="s">
-        <v>1164</v>
+        <v>1027</v>
       </c>
       <c r="I25" t="s">
-        <v>1185</v>
+        <v>1048</v>
       </c>
       <c r="J25" t="s">
-        <v>1128</v>
+        <v>991</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -9484,31 +8376,31 @@
         <v>20330051920383</v>
       </c>
       <c r="B26" t="s">
-        <v>286</v>
+        <v>449</v>
       </c>
       <c r="C26" t="s">
         <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>1079</v>
+        <v>942</v>
       </c>
       <c r="E26" t="s">
-        <v>1104</v>
+        <v>967</v>
       </c>
       <c r="F26" t="s">
-        <v>1129</v>
+        <v>992</v>
       </c>
       <c r="G26" t="s">
-        <v>1140</v>
+        <v>1003</v>
       </c>
       <c r="H26" t="s">
-        <v>1165</v>
+        <v>1028</v>
       </c>
       <c r="I26" t="s">
-        <v>1186</v>
+        <v>1049</v>
       </c>
       <c r="J26" t="s">
-        <v>1205</v>
+        <v>1068</v>
       </c>
     </row>
   </sheetData>
